--- a/artifacts/reports/architecture_tuning_esn_v1.xlsx
+++ b/artifacts/reports/architecture_tuning_esn_v1.xlsx
@@ -442,7 +442,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>architecture_tuning_esn_v1_20260329T153803Z</t>
+          <t>architecture_tuning_esn_v1_20260819T074659Z</t>
         </is>
       </c>
     </row>
@@ -561,7 +561,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.02753867376085088</v>
+        <v>0.02723695678767786</v>
       </c>
     </row>
     <row r="14">
@@ -571,7 +571,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.01034137666237373</v>
+        <v>0.01033782885424267</v>
       </c>
     </row>
     <row r="15">
@@ -581,7 +581,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>19.81209993609486</v>
+        <v>22.85509424444859</v>
       </c>
     </row>
     <row r="16">
@@ -591,7 +591,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>17.11151140014408</v>
+        <v>19.70738704997348</v>
       </c>
     </row>
     <row r="17">
@@ -850,7 +850,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y37"/>
+  <dimension ref="A1:AJ37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -916,65 +916,120 @@
       </c>
       <c r="M1" t="inlineStr">
         <is>
+          <t>hidden_size</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>num_layers</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>dropout</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>train_r</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>beta</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>r_min</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>r_max</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>hidden_dims</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>depth</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
           <t>params_json</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>params_repr</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>n_series</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>horizon</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>mae_mean</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>rmse_mean</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>mase_mean</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>directional_accuracy_mean</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>fit_time_sec_mean</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>predict_time_sec_mean</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
+        <is>
+          <t>fit_time</t>
+        </is>
+      </c>
+      <c r="AG1" t="inlineStr">
+        <is>
+          <t>predict_time</t>
+        </is>
+      </c>
+      <c r="AH1" t="inlineStr">
         <is>
           <t>total_runtime_sec</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>status</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>notes</t>
         </is>
@@ -983,7 +1038,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>architecture_tuning_esn_v1_20260329T153803Z</t>
+          <t>architecture_tuning_esn_v1_20260819T074659Z</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1019,54 +1074,69 @@
       </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr"/>
+      <c r="V2" t="inlineStr">
         <is>
           <t>{"compare_group_id": "esn_grp_001", "model_params": {"input_scale": 0.1, "leak_rate": 1.0, "n_reservoir": 64, "ridge_alpha": 0.0001, "seed": 2026, "spectral_radius": 0.9}, "runtime_params": {}}</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>{'model_params': {'n_reservoir': 64, 'spectral_radius': 0.9, 'input_scale': 0.1, 'leak_rate': 1.0, 'ridge_alpha': 0.0001, 'seed': 2026}, 'runtime_params': {}, 'compare_group_id': 'esn_grp_001'}</t>
         </is>
       </c>
-      <c r="O2" t="n">
+      <c r="X2" t="n">
         <v>12</v>
       </c>
-      <c r="P2" t="n">
+      <c r="Y2" t="n">
         <v>1</v>
       </c>
-      <c r="Q2" t="n">
-        <v>0.01039454830934849</v>
-      </c>
-      <c r="R2" t="n">
-        <v>0.01436768173870237</v>
-      </c>
-      <c r="S2" t="n">
-        <v>0.6820256255959546</v>
-      </c>
-      <c r="T2" t="n">
-        <v>0.5028320986192303</v>
-      </c>
-      <c r="U2" t="n">
-        <v>0.4321654500025842</v>
-      </c>
-      <c r="V2" t="n">
-        <v>0.269285669437118</v>
-      </c>
-      <c r="W2" t="n">
-        <v>25.25224029982928</v>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>success</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr"/>
+      <c r="Z2" t="n">
+        <v>0.01039268599059335</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>0.01435569111938743</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.6822100770592946</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>0.5002666903254956</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>0.553755733332461</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>0.2741491944466866</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>0.553755733332461</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>0.2741491944466866</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>29.80457740004931</v>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>architecture_tuning_esn_v1_20260329T153803Z</t>
+          <t>architecture_tuning_esn_v1_20260819T074659Z</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1102,54 +1172,69 @@
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr"/>
+      <c r="S3" t="inlineStr"/>
+      <c r="T3" t="inlineStr"/>
+      <c r="U3" t="inlineStr"/>
+      <c r="V3" t="inlineStr">
         <is>
           <t>{"compare_group_id": "esn_grp_001", "model_params": {"input_scale": 0.1, "leak_rate": 1.0, "n_reservoir": 64, "ridge_alpha": 0.0001, "seed": 2026, "spectral_radius": 0.9}, "runtime_params": {}}</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>{'model_params': {'n_reservoir': 64, 'spectral_radius': 0.9, 'input_scale': 0.1, 'leak_rate': 1.0, 'ridge_alpha': 0.0001, 'seed': 2026}, 'runtime_params': {}, 'compare_group_id': 'esn_grp_001'}</t>
         </is>
       </c>
-      <c r="O3" t="n">
+      <c r="X3" t="n">
         <v>12</v>
       </c>
-      <c r="P3" t="n">
+      <c r="Y3" t="n">
         <v>5</v>
       </c>
-      <c r="Q3" t="n">
-        <v>0.02330462272532673</v>
-      </c>
-      <c r="R3" t="n">
-        <v>0.03140757195228856</v>
-      </c>
-      <c r="S3" t="n">
-        <v>1.557967370746257</v>
-      </c>
-      <c r="T3" t="n">
-        <v>0.5142186926229845</v>
-      </c>
-      <c r="U3" t="n">
-        <v>0.2200205222211985</v>
-      </c>
-      <c r="V3" t="n">
-        <v>0.1373269750005824</v>
-      </c>
-      <c r="W3" t="n">
-        <v>12.86450989998411</v>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>success</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr"/>
+      <c r="Z3" t="n">
+        <v>0.02314510117570092</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>0.0312086568657424</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>1.535114208958263</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>0.5211481108206731</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>0.2816471555565335</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>0.1407738250001987</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>0.2816471555565335</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>0.1407738250001987</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>15.20715530004236</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>architecture_tuning_esn_v1_20260329T153803Z</t>
+          <t>architecture_tuning_esn_v1_20260819T074659Z</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1185,54 +1270,69 @@
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="inlineStr"/>
+      <c r="T4" t="inlineStr"/>
+      <c r="U4" t="inlineStr"/>
+      <c r="V4" t="inlineStr">
         <is>
           <t>{"compare_group_id": "esn_grp_001", "model_params": {"input_scale": 0.1, "leak_rate": 1.0, "n_reservoir": 64, "ridge_alpha": 0.0001, "seed": 2026, "spectral_radius": 0.9}, "runtime_params": {}}</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>{'model_params': {'n_reservoir': 64, 'spectral_radius': 0.9, 'input_scale': 0.1, 'leak_rate': 1.0, 'ridge_alpha': 0.0001, 'seed': 2026}, 'runtime_params': {}, 'compare_group_id': 'esn_grp_001'}</t>
         </is>
       </c>
-      <c r="O4" t="n">
+      <c r="X4" t="n">
         <v>12</v>
       </c>
-      <c r="P4" t="n">
+      <c r="Y4" t="n">
         <v>20</v>
       </c>
-      <c r="Q4" t="n">
-        <v>0.04768954333195959</v>
-      </c>
-      <c r="R4" t="n">
-        <v>0.06154801970929421</v>
-      </c>
-      <c r="S4" t="n">
-        <v>3.187976837845405</v>
-      </c>
-      <c r="T4" t="n">
-        <v>0.4947285293643163</v>
-      </c>
-      <c r="U4" t="n">
-        <v>0.1104597555434642</v>
-      </c>
-      <c r="V4" t="n">
-        <v>0.06862462778291148</v>
-      </c>
-      <c r="W4" t="n">
-        <v>6.447037799749523</v>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>success</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr"/>
+      <c r="Z4" t="n">
+        <v>0.04711416704780948</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>0.06091774773536213</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>3.116200502491193</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>0.515789004768522</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>0.1376069416651767</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>0.06961552500029534</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>0.1376069416651767</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>0.06961552500029534</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>7.460008799956995</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>architecture_tuning_esn_v1_20260329T153803Z</t>
+          <t>architecture_tuning_esn_v1_20260819T074659Z</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1268,54 +1368,69 @@
       </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr"/>
+      <c r="T5" t="inlineStr"/>
+      <c r="U5" t="inlineStr"/>
+      <c r="V5" t="inlineStr">
         <is>
           <t>{"compare_group_id": "esn_grp_002", "model_params": {"input_scale": 0.1, "leak_rate": 0.8, "n_reservoir": 96, "ridge_alpha": 0.0001, "seed": 2026, "spectral_radius": 0.95}, "runtime_params": {}}</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>{'model_params': {'n_reservoir': 96, 'spectral_radius': 0.95, 'input_scale': 0.1, 'leak_rate': 0.8, 'ridge_alpha': 0.0001, 'seed': 2026}, 'runtime_params': {}, 'compare_group_id': 'esn_grp_002'}</t>
         </is>
       </c>
-      <c r="O5" t="n">
+      <c r="X5" t="n">
         <v>12</v>
       </c>
-      <c r="P5" t="n">
+      <c r="Y5" t="n">
         <v>1</v>
       </c>
-      <c r="Q5" t="n">
-        <v>0.01036761460764232</v>
-      </c>
-      <c r="R5" t="n">
-        <v>0.01433636669840518</v>
-      </c>
-      <c r="S5" t="n">
-        <v>0.6796647759153229</v>
-      </c>
-      <c r="T5" t="n">
-        <v>0.5039032153473144</v>
-      </c>
-      <c r="U5" t="n">
-        <v>0.4881838444400475</v>
-      </c>
-      <c r="V5" t="n">
-        <v>0.3018619277799088</v>
-      </c>
-      <c r="W5" t="n">
-        <v>28.44164779991843</v>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>success</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr"/>
+      <c r="Z5" t="n">
+        <v>0.0103593698603878</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>0.0143156113828853</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.6794561775633531</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>0.500474270167374</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>0.6241629444444293</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>0.3106009027784846</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>0.6241629444444293</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>0.3106009027784846</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>33.6514985000249</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>architecture_tuning_esn_v1_20260329T153803Z</t>
+          <t>architecture_tuning_esn_v1_20260819T074659Z</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1351,54 +1466,69 @@
       </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="inlineStr"/>
+      <c r="T6" t="inlineStr"/>
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="inlineStr">
         <is>
           <t>{"compare_group_id": "esn_grp_002", "model_params": {"input_scale": 0.1, "leak_rate": 0.8, "n_reservoir": 96, "ridge_alpha": 0.0001, "seed": 2026, "spectral_radius": 0.95}, "runtime_params": {}}</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>{'model_params': {'n_reservoir': 96, 'spectral_radius': 0.95, 'input_scale': 0.1, 'leak_rate': 0.8, 'ridge_alpha': 0.0001, 'seed': 2026}, 'runtime_params': {}, 'compare_group_id': 'esn_grp_002'}</t>
         </is>
       </c>
-      <c r="O6" t="n">
+      <c r="X6" t="n">
         <v>12</v>
       </c>
-      <c r="P6" t="n">
+      <c r="Y6" t="n">
         <v>5</v>
       </c>
-      <c r="Q6" t="n">
-        <v>0.02331971317695284</v>
-      </c>
-      <c r="R6" t="n">
-        <v>0.03142107448277961</v>
-      </c>
-      <c r="S6" t="n">
-        <v>1.563176034403357</v>
-      </c>
-      <c r="T6" t="n">
-        <v>0.5154013666419962</v>
-      </c>
-      <c r="U6" t="n">
-        <v>0.2484834694348845</v>
-      </c>
-      <c r="V6" t="n">
-        <v>0.1554425944276671</v>
-      </c>
-      <c r="W6" t="n">
-        <v>14.54133829905186</v>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>success</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr"/>
+      <c r="Z6" t="n">
+        <v>0.02314467726245402</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>0.03120718262159135</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>1.535861139823535</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>0.5181447504134895</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>0.3110522861113875</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>0.1563249777779371</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>0.3110522861113875</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>0.1563249777779371</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>16.82558150001569</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>architecture_tuning_esn_v1_20260329T153803Z</t>
+          <t>architecture_tuning_esn_v1_20260819T074659Z</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1434,54 +1564,69 @@
       </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr"/>
+      <c r="S7" t="inlineStr"/>
+      <c r="T7" t="inlineStr"/>
+      <c r="U7" t="inlineStr"/>
+      <c r="V7" t="inlineStr">
         <is>
           <t>{"compare_group_id": "esn_grp_002", "model_params": {"input_scale": 0.1, "leak_rate": 0.8, "n_reservoir": 96, "ridge_alpha": 0.0001, "seed": 2026, "spectral_radius": 0.95}, "runtime_params": {}}</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>{'model_params': {'n_reservoir': 96, 'spectral_radius': 0.95, 'input_scale': 0.1, 'leak_rate': 0.8, 'ridge_alpha': 0.0001, 'seed': 2026}, 'runtime_params': {}, 'compare_group_id': 'esn_grp_002'}</t>
         </is>
       </c>
-      <c r="O7" t="n">
+      <c r="X7" t="n">
         <v>12</v>
       </c>
-      <c r="P7" t="n">
+      <c r="Y7" t="n">
         <v>20</v>
       </c>
-      <c r="Q7" t="n">
-        <v>0.04771501819164769</v>
-      </c>
-      <c r="R7" t="n">
-        <v>0.06156715474599504</v>
-      </c>
-      <c r="S7" t="n">
-        <v>3.189741277319856</v>
-      </c>
-      <c r="T7" t="n">
-        <v>0.4955321714480752</v>
-      </c>
-      <c r="U7" t="n">
-        <v>0.1236389333336976</v>
-      </c>
-      <c r="V7" t="n">
-        <v>0.0770179055560018</v>
-      </c>
-      <c r="W7" t="n">
-        <v>7.223646200029179</v>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>success</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr"/>
+      <c r="Z7" t="n">
+        <v>0.04715806020447764</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>0.06094869873423279</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>3.117999473340024</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>0.5172464815266645</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>0.1544547638897913</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>0.07819931666542997</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>0.1544547638897913</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>0.07819931666542997</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>8.375546899987967</v>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>architecture_tuning_esn_v1_20260329T153803Z</t>
+          <t>architecture_tuning_esn_v1_20260819T074659Z</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1517,54 +1662,69 @@
       </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr"/>
+      <c r="S8" t="inlineStr"/>
+      <c r="T8" t="inlineStr"/>
+      <c r="U8" t="inlineStr"/>
+      <c r="V8" t="inlineStr">
         <is>
           <t>{"compare_group_id": "esn_grp_003", "model_params": {"input_scale": 0.08, "leak_rate": 0.7, "n_reservoir": 128, "ridge_alpha": 0.0005, "seed": 2026, "spectral_radius": 0.98}, "runtime_params": {}}</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>{'model_params': {'n_reservoir': 128, 'spectral_radius': 0.98, 'input_scale': 0.08, 'leak_rate': 0.7, 'ridge_alpha': 0.0005, 'seed': 2026}, 'runtime_params': {}, 'compare_group_id': 'esn_grp_003'}</t>
         </is>
       </c>
-      <c r="O8" t="n">
+      <c r="X8" t="n">
         <v>12</v>
       </c>
-      <c r="P8" t="n">
+      <c r="Y8" t="n">
         <v>1</v>
       </c>
-      <c r="Q8" t="n">
-        <v>0.01034137666237373</v>
-      </c>
-      <c r="R8" t="n">
-        <v>0.01429137021584309</v>
-      </c>
-      <c r="S8" t="n">
-        <v>0.6773609985805448</v>
-      </c>
-      <c r="T8" t="n">
-        <v>0.507183991941757</v>
-      </c>
-      <c r="U8" t="n">
-        <v>0.5762485083347807</v>
-      </c>
-      <c r="V8" t="n">
-        <v>0.357775774988113</v>
-      </c>
-      <c r="W8" t="n">
-        <v>33.62487419962417</v>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>success</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr"/>
+      <c r="Z8" t="n">
+        <v>0.01033782885424267</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>0.01427699509113673</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0.6774907023916258</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>0.504831246683341</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>0.7252683361107807</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>0.3574251083320835</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>0.7252683361107807</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>0.3574251083320835</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>38.97696399994311</v>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>architecture_tuning_esn_v1_20260329T153803Z</t>
+          <t>architecture_tuning_esn_v1_20260819T074659Z</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1600,54 +1760,69 @@
       </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr"/>
+      <c r="S9" t="inlineStr"/>
+      <c r="T9" t="inlineStr"/>
+      <c r="U9" t="inlineStr"/>
+      <c r="V9" t="inlineStr">
         <is>
           <t>{"compare_group_id": "esn_grp_003", "model_params": {"input_scale": 0.08, "leak_rate": 0.7, "n_reservoir": 128, "ridge_alpha": 0.0005, "seed": 2026, "spectral_radius": 0.98}, "runtime_params": {}}</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>{'model_params': {'n_reservoir': 128, 'spectral_radius': 0.98, 'input_scale': 0.08, 'leak_rate': 0.7, 'ridge_alpha': 0.0005, 'seed': 2026}, 'runtime_params': {}, 'compare_group_id': 'esn_grp_003'}</t>
         </is>
       </c>
-      <c r="O9" t="n">
+      <c r="X9" t="n">
         <v>12</v>
       </c>
-      <c r="P9" t="n">
+      <c r="Y9" t="n">
         <v>5</v>
       </c>
-      <c r="Q9" t="n">
-        <v>0.02328078903148209</v>
-      </c>
-      <c r="R9" t="n">
-        <v>0.03138889440743375</v>
-      </c>
-      <c r="S9" t="n">
-        <v>1.556589419404968</v>
-      </c>
-      <c r="T9" t="n">
-        <v>0.5155740776203771</v>
-      </c>
-      <c r="U9" t="n">
-        <v>0.2949133416663648</v>
-      </c>
-      <c r="V9" t="n">
-        <v>0.1818892972207524</v>
-      </c>
-      <c r="W9" t="n">
-        <v>17.16489499993622</v>
-      </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>success</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr"/>
+      <c r="Z9" t="n">
+        <v>0.02312797301778825</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>0.03120546640553222</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>1.534209239793129</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>0.5207246059184888</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>0.3671198777766323</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>0.182409219443798</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>0.3671198777766323</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>0.182409219443798</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>19.78304749993549</v>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>architecture_tuning_esn_v1_20260329T153803Z</t>
+          <t>architecture_tuning_esn_v1_20260819T074659Z</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1683,54 +1858,69 @@
       </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="inlineStr"/>
+      <c r="S10" t="inlineStr"/>
+      <c r="T10" t="inlineStr"/>
+      <c r="U10" t="inlineStr"/>
+      <c r="V10" t="inlineStr">
         <is>
           <t>{"compare_group_id": "esn_grp_003", "model_params": {"input_scale": 0.08, "leak_rate": 0.7, "n_reservoir": 128, "ridge_alpha": 0.0005, "seed": 2026, "spectral_radius": 0.98}, "runtime_params": {}}</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>{'model_params': {'n_reservoir': 128, 'spectral_radius': 0.98, 'input_scale': 0.08, 'leak_rate': 0.7, 'ridge_alpha': 0.0005, 'seed': 2026}, 'runtime_params': {}, 'compare_group_id': 'esn_grp_003'}</t>
         </is>
       </c>
-      <c r="O10" t="n">
+      <c r="X10" t="n">
         <v>12</v>
       </c>
-      <c r="P10" t="n">
+      <c r="Y10" t="n">
         <v>20</v>
       </c>
-      <c r="Q10" t="n">
-        <v>0.04776794316810811</v>
-      </c>
-      <c r="R10" t="n">
-        <v>0.06157144711009622</v>
-      </c>
-      <c r="S10" t="n">
-        <v>3.189603833897907</v>
-      </c>
-      <c r="T10" t="n">
-        <v>0.4949967459426243</v>
-      </c>
-      <c r="U10" t="n">
-        <v>0.147321661109648</v>
-      </c>
-      <c r="V10" t="n">
-        <v>0.09123454444084524</v>
-      </c>
-      <c r="W10" t="n">
-        <v>8.588023399817757</v>
-      </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>success</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr"/>
+      <c r="Z10" t="n">
+        <v>0.04725686013581028</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>0.06102888627049385</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>3.119899582945399</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>0.5171152271366489</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>0.181870272223427</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>0.09056761111019618</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>0.181870272223427</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>0.09056761111019618</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>9.807763800010434</v>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>architecture_tuning_esn_v1_20260329T153803Z</t>
+          <t>architecture_tuning_esn_v1_20260819T074659Z</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1766,54 +1956,69 @@
       </c>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="inlineStr"/>
+      <c r="S11" t="inlineStr"/>
+      <c r="T11" t="inlineStr"/>
+      <c r="U11" t="inlineStr"/>
+      <c r="V11" t="inlineStr">
         <is>
           <t>{"compare_group_id": "esn_grp_004", "model_params": {"input_scale": 0.12, "leak_rate": 0.9, "n_reservoir": 160, "ridge_alpha": 0.001, "seed": 2026, "spectral_radius": 0.92}, "runtime_params": {}}</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>{'model_params': {'n_reservoir': 160, 'spectral_radius': 0.92, 'input_scale': 0.12, 'leak_rate': 0.9, 'ridge_alpha': 0.001, 'seed': 2026}, 'runtime_params': {}, 'compare_group_id': 'esn_grp_004'}</t>
         </is>
       </c>
-      <c r="O11" t="n">
+      <c r="X11" t="n">
         <v>12</v>
       </c>
-      <c r="P11" t="n">
+      <c r="Y11" t="n">
         <v>1</v>
       </c>
-      <c r="Q11" t="n">
-        <v>0.01035285634382571</v>
-      </c>
-      <c r="R11" t="n">
-        <v>0.01431152315879061</v>
-      </c>
-      <c r="S11" t="n">
-        <v>0.678352338223743</v>
-      </c>
-      <c r="T11" t="n">
-        <v>0.5029487639329754</v>
-      </c>
-      <c r="U11" t="n">
-        <v>0.6753047555555693</v>
-      </c>
-      <c r="V11" t="n">
-        <v>0.4175884222204331</v>
-      </c>
-      <c r="W11" t="n">
-        <v>39.34415439993609</v>
-      </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>success</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr"/>
+      <c r="Z11" t="n">
+        <v>0.01034924599642818</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>0.01429968034150704</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0.6784298273945705</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>0.5031028617348355</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>0.8307366805553708</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>0.4111477638879377</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>0.8307366805553708</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>0.4111477638879377</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>44.70783999995911</v>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>architecture_tuning_esn_v1_20260329T153803Z</t>
+          <t>architecture_tuning_esn_v1_20260819T074659Z</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1849,54 +2054,69 @@
       </c>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="inlineStr"/>
+      <c r="S12" t="inlineStr"/>
+      <c r="T12" t="inlineStr"/>
+      <c r="U12" t="inlineStr"/>
+      <c r="V12" t="inlineStr">
         <is>
           <t>{"compare_group_id": "esn_grp_004", "model_params": {"input_scale": 0.12, "leak_rate": 0.9, "n_reservoir": 160, "ridge_alpha": 0.001, "seed": 2026, "spectral_radius": 0.92}, "runtime_params": {}}</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr">
+      <c r="W12" t="inlineStr">
         <is>
           <t>{'model_params': {'n_reservoir': 160, 'spectral_radius': 0.92, 'input_scale': 0.12, 'leak_rate': 0.9, 'ridge_alpha': 0.001, 'seed': 2026}, 'runtime_params': {}, 'compare_group_id': 'esn_grp_004'}</t>
         </is>
       </c>
-      <c r="O12" t="n">
+      <c r="X12" t="n">
         <v>12</v>
       </c>
-      <c r="P12" t="n">
+      <c r="Y12" t="n">
         <v>5</v>
       </c>
-      <c r="Q12" t="n">
-        <v>0.02316324249823553</v>
-      </c>
-      <c r="R12" t="n">
-        <v>0.03123117432855536</v>
-      </c>
-      <c r="S12" t="n">
-        <v>1.539045132707624</v>
-      </c>
-      <c r="T12" t="n">
-        <v>0.5135002732595695</v>
-      </c>
-      <c r="U12" t="n">
-        <v>0.3419074166740756</v>
-      </c>
-      <c r="V12" t="n">
-        <v>0.2125711499894452</v>
-      </c>
-      <c r="W12" t="n">
-        <v>19.96122839988675</v>
-      </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>success</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr"/>
+      <c r="Z12" t="n">
+        <v>0.02312004313611583</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>0.0311582045370359</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>1.533552753962528</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>0.5146844711194423</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>0.4276182222214023</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>0.2106089944443536</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>0.4276182222214023</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>0.2106089944443536</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>22.97617979996721</v>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>architecture_tuning_esn_v1_20260329T153803Z</t>
+          <t>architecture_tuning_esn_v1_20260819T074659Z</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1932,54 +2152,69 @@
       </c>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr"/>
+      <c r="Q13" t="inlineStr"/>
+      <c r="R13" t="inlineStr"/>
+      <c r="S13" t="inlineStr"/>
+      <c r="T13" t="inlineStr"/>
+      <c r="U13" t="inlineStr"/>
+      <c r="V13" t="inlineStr">
         <is>
           <t>{"compare_group_id": "esn_grp_004", "model_params": {"input_scale": 0.12, "leak_rate": 0.9, "n_reservoir": 160, "ridge_alpha": 0.001, "seed": 2026, "spectral_radius": 0.92}, "runtime_params": {}}</t>
         </is>
       </c>
-      <c r="N13" t="inlineStr">
+      <c r="W13" t="inlineStr">
         <is>
           <t>{'model_params': {'n_reservoir': 160, 'spectral_radius': 0.92, 'input_scale': 0.12, 'leak_rate': 0.9, 'ridge_alpha': 0.001, 'seed': 2026}, 'runtime_params': {}, 'compare_group_id': 'esn_grp_004'}</t>
         </is>
       </c>
-      <c r="O13" t="n">
+      <c r="X13" t="n">
         <v>12</v>
       </c>
-      <c r="P13" t="n">
+      <c r="Y13" t="n">
         <v>20</v>
       </c>
-      <c r="Q13" t="n">
-        <v>0.04772484293579016</v>
-      </c>
-      <c r="R13" t="n">
-        <v>0.06152866527465806</v>
-      </c>
-      <c r="S13" t="n">
-        <v>3.182544335598505</v>
-      </c>
-      <c r="T13" t="n">
-        <v>0.4945451846872007</v>
-      </c>
-      <c r="U13" t="n">
-        <v>0.1698113055511688</v>
-      </c>
-      <c r="V13" t="n">
-        <v>0.1043188499978795</v>
-      </c>
-      <c r="W13" t="n">
-        <v>9.86868559976574</v>
-      </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>success</t>
-        </is>
-      </c>
-      <c r="Y13" t="inlineStr"/>
+      <c r="Z13" t="n">
+        <v>0.04722205340026055</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>0.06099215103288493</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>3.11471283271913</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>0.5172218772652118</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>0.2120112444451176</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>0.1046416583327906</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>0.2120112444451176</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>0.1046416583327906</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>11.3995045000047</v>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="AJ13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>architecture_tuning_esn_v1_20260329T153803Z</t>
+          <t>architecture_tuning_esn_v1_20260819T074659Z</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -2017,54 +2252,69 @@
       </c>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="inlineStr"/>
+      <c r="S14" t="inlineStr"/>
+      <c r="T14" t="inlineStr"/>
+      <c r="U14" t="inlineStr"/>
+      <c r="V14" t="inlineStr">
         <is>
           <t>{"compare_group_id": "esn_grp_001", "model_params": {"chaotic_spectral_radius": 1.2, "input_scale": 0.1, "leak_rate": 1.0, "n_reservoir": 64, "ridge_alpha": 0.0001, "seed": 2026, "spectral_radius": 0.9}, "runtime_params": {}}</t>
         </is>
       </c>
-      <c r="N14" t="inlineStr">
+      <c r="W14" t="inlineStr">
         <is>
           <t>{'model_params': {'n_reservoir': 64, 'spectral_radius': 0.9, 'chaotic_spectral_radius': 1.2, 'input_scale': 0.1, 'leak_rate': 1.0, 'ridge_alpha': 0.0001, 'seed': 2026}, 'runtime_params': {}, 'compare_group_id': 'esn_grp_001'}</t>
         </is>
       </c>
-      <c r="O14" t="n">
+      <c r="X14" t="n">
         <v>12</v>
       </c>
-      <c r="P14" t="n">
+      <c r="Y14" t="n">
         <v>1</v>
       </c>
-      <c r="Q14" t="n">
-        <v>0.01099948145462603</v>
-      </c>
-      <c r="R14" t="n">
-        <v>0.01553690942022753</v>
-      </c>
-      <c r="S14" t="n">
-        <v>0.7191475790261573</v>
-      </c>
-      <c r="T14" t="n">
-        <v>0.4996293329807145</v>
-      </c>
-      <c r="U14" t="n">
-        <v>0.4336332444347337</v>
-      </c>
-      <c r="V14" t="n">
-        <v>0.2700599166791006</v>
-      </c>
-      <c r="W14" t="n">
-        <v>25.33295380009804</v>
-      </c>
-      <c r="X14" t="inlineStr">
-        <is>
-          <t>success</t>
-        </is>
-      </c>
-      <c r="Y14" t="inlineStr"/>
+      <c r="Z14" t="n">
+        <v>0.01086151268305805</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>0.01521956050357054</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>0.7106525767747849</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>0.492836492482644</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>0.54235616944263</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>0.2703841694447975</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>0.54235616944263</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>0.2703841694447975</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>29.25865219994739</v>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="AJ14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>architecture_tuning_esn_v1_20260329T153803Z</t>
+          <t>architecture_tuning_esn_v1_20260819T074659Z</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2102,54 +2352,69 @@
       </c>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" t="inlineStr"/>
+      <c r="Q15" t="inlineStr"/>
+      <c r="R15" t="inlineStr"/>
+      <c r="S15" t="inlineStr"/>
+      <c r="T15" t="inlineStr"/>
+      <c r="U15" t="inlineStr"/>
+      <c r="V15" t="inlineStr">
         <is>
           <t>{"compare_group_id": "esn_grp_001", "model_params": {"chaotic_spectral_radius": 1.2, "input_scale": 0.1, "leak_rate": 1.0, "n_reservoir": 64, "ridge_alpha": 0.0001, "seed": 2026, "spectral_radius": 0.9}, "runtime_params": {}}</t>
         </is>
       </c>
-      <c r="N15" t="inlineStr">
+      <c r="W15" t="inlineStr">
         <is>
           <t>{'model_params': {'n_reservoir': 64, 'spectral_radius': 0.9, 'chaotic_spectral_radius': 1.2, 'input_scale': 0.1, 'leak_rate': 1.0, 'ridge_alpha': 0.0001, 'seed': 2026}, 'runtime_params': {}, 'compare_group_id': 'esn_grp_001'}</t>
         </is>
       </c>
-      <c r="O15" t="n">
+      <c r="X15" t="n">
         <v>12</v>
       </c>
-      <c r="P15" t="n">
+      <c r="Y15" t="n">
         <v>5</v>
       </c>
-      <c r="Q15" t="n">
-        <v>0.02479065188700861</v>
-      </c>
-      <c r="R15" t="n">
-        <v>0.0332120190177705</v>
-      </c>
-      <c r="S15" t="n">
-        <v>1.688271995118107</v>
-      </c>
-      <c r="T15" t="n">
-        <v>0.5012636397141818</v>
-      </c>
-      <c r="U15" t="n">
-        <v>0.2205932055528844</v>
-      </c>
-      <c r="V15" t="n">
-        <v>0.1372099999894595</v>
-      </c>
-      <c r="W15" t="n">
-        <v>12.88091539952438</v>
-      </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>success</t>
-        </is>
-      </c>
-      <c r="Y15" t="inlineStr"/>
+      <c r="Z15" t="n">
+        <v>0.02444551875570298</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>0.03280192422069964</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>1.640674432850307</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>0.5023826311093357</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>0.2757412222223743</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>0.1383941833317092</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>0.2757412222223743</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>0.1383941833317092</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>14.90887459994701</v>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="AJ15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>architecture_tuning_esn_v1_20260329T153803Z</t>
+          <t>architecture_tuning_esn_v1_20260819T074659Z</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2187,54 +2452,69 @@
       </c>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" t="inlineStr"/>
+      <c r="Q16" t="inlineStr"/>
+      <c r="R16" t="inlineStr"/>
+      <c r="S16" t="inlineStr"/>
+      <c r="T16" t="inlineStr"/>
+      <c r="U16" t="inlineStr"/>
+      <c r="V16" t="inlineStr">
         <is>
           <t>{"compare_group_id": "esn_grp_001", "model_params": {"chaotic_spectral_radius": 1.2, "input_scale": 0.1, "leak_rate": 1.0, "n_reservoir": 64, "ridge_alpha": 0.0001, "seed": 2026, "spectral_radius": 0.9}, "runtime_params": {}}</t>
         </is>
       </c>
-      <c r="N16" t="inlineStr">
+      <c r="W16" t="inlineStr">
         <is>
           <t>{'model_params': {'n_reservoir': 64, 'spectral_radius': 0.9, 'chaotic_spectral_radius': 1.2, 'input_scale': 0.1, 'leak_rate': 1.0, 'ridge_alpha': 0.0001, 'seed': 2026}, 'runtime_params': {}, 'compare_group_id': 'esn_grp_001'}</t>
         </is>
       </c>
-      <c r="O16" t="n">
+      <c r="X16" t="n">
         <v>12</v>
       </c>
-      <c r="P16" t="n">
+      <c r="Y16" t="n">
         <v>20</v>
       </c>
-      <c r="Q16" t="n">
-        <v>0.04991233402531026</v>
-      </c>
-      <c r="R16" t="n">
-        <v>0.06476111057317578</v>
-      </c>
-      <c r="S16" t="n">
-        <v>3.342262562085108</v>
-      </c>
-      <c r="T16" t="n">
-        <v>0.5077951211990984</v>
-      </c>
-      <c r="U16" t="n">
-        <v>0.1107080000025841</v>
-      </c>
-      <c r="V16" t="n">
-        <v>0.0689723416710169</v>
-      </c>
-      <c r="W16" t="n">
-        <v>6.468492300249636</v>
-      </c>
-      <c r="X16" t="inlineStr">
-        <is>
-          <t>success</t>
-        </is>
-      </c>
-      <c r="Y16" t="inlineStr"/>
+      <c r="Z16" t="n">
+        <v>0.04893294690021489</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>0.06408061966586349</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>3.253643036080499</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>0.5107041986954325</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>0.1347647583340101</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>0.06840248333214226</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>0.1347647583340101</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>0.06840248333214226</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>7.314020699981484</v>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="AJ16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>architecture_tuning_esn_v1_20260329T153803Z</t>
+          <t>architecture_tuning_esn_v1_20260819T074659Z</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2272,54 +2552,69 @@
       </c>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="inlineStr"/>
+      <c r="P17" t="inlineStr"/>
+      <c r="Q17" t="inlineStr"/>
+      <c r="R17" t="inlineStr"/>
+      <c r="S17" t="inlineStr"/>
+      <c r="T17" t="inlineStr"/>
+      <c r="U17" t="inlineStr"/>
+      <c r="V17" t="inlineStr">
         <is>
           <t>{"compare_group_id": "esn_grp_002", "model_params": {"chaotic_spectral_radius": 1.25, "input_scale": 0.1, "leak_rate": 0.8, "n_reservoir": 96, "ridge_alpha": 0.0001, "seed": 2026, "spectral_radius": 0.95}, "runtime_params": {}}</t>
         </is>
       </c>
-      <c r="N17" t="inlineStr">
+      <c r="W17" t="inlineStr">
         <is>
           <t>{'model_params': {'n_reservoir': 96, 'spectral_radius': 0.95, 'chaotic_spectral_radius': 1.25, 'input_scale': 0.1, 'leak_rate': 0.8, 'ridge_alpha': 0.0001, 'seed': 2026}, 'runtime_params': {}, 'compare_group_id': 'esn_grp_002'}</t>
         </is>
       </c>
-      <c r="O17" t="n">
+      <c r="X17" t="n">
         <v>12</v>
       </c>
-      <c r="P17" t="n">
+      <c r="Y17" t="n">
         <v>1</v>
       </c>
-      <c r="Q17" t="n">
-        <v>0.01063166951982817</v>
-      </c>
-      <c r="R17" t="n">
-        <v>0.01473016845151821</v>
-      </c>
-      <c r="S17" t="n">
-        <v>0.6957751801022097</v>
-      </c>
-      <c r="T17" t="n">
-        <v>0.5007984906462047</v>
-      </c>
-      <c r="U17" t="n">
-        <v>0.4839761277673664</v>
-      </c>
-      <c r="V17" t="n">
-        <v>0.3019129888853059</v>
-      </c>
-      <c r="W17" t="n">
-        <v>28.29200819949619</v>
-      </c>
-      <c r="X17" t="inlineStr">
-        <is>
-          <t>success</t>
-        </is>
-      </c>
-      <c r="Y17" t="inlineStr"/>
+      <c r="Z17" t="n">
+        <v>0.01053668461277604</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>0.01453785894297915</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>0.6912171500733124</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>0.4997423890500503</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>0.6039024305553337</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>0.3015761888879449</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>0.6039024305553337</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>0.3015761888879449</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>32.59723029995803</v>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="AJ17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>architecture_tuning_esn_v1_20260329T153803Z</t>
+          <t>architecture_tuning_esn_v1_20260819T074659Z</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2357,54 +2652,69 @@
       </c>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="inlineStr"/>
+      <c r="P18" t="inlineStr"/>
+      <c r="Q18" t="inlineStr"/>
+      <c r="R18" t="inlineStr"/>
+      <c r="S18" t="inlineStr"/>
+      <c r="T18" t="inlineStr"/>
+      <c r="U18" t="inlineStr"/>
+      <c r="V18" t="inlineStr">
         <is>
           <t>{"compare_group_id": "esn_grp_002", "model_params": {"chaotic_spectral_radius": 1.25, "input_scale": 0.1, "leak_rate": 0.8, "n_reservoir": 96, "ridge_alpha": 0.0001, "seed": 2026, "spectral_radius": 0.95}, "runtime_params": {}}</t>
         </is>
       </c>
-      <c r="N18" t="inlineStr">
+      <c r="W18" t="inlineStr">
         <is>
           <t>{'model_params': {'n_reservoir': 96, 'spectral_radius': 0.95, 'chaotic_spectral_radius': 1.25, 'input_scale': 0.1, 'leak_rate': 0.8, 'ridge_alpha': 0.0001, 'seed': 2026}, 'runtime_params': {}, 'compare_group_id': 'esn_grp_002'}</t>
         </is>
       </c>
-      <c r="O18" t="n">
+      <c r="X18" t="n">
         <v>12</v>
       </c>
-      <c r="P18" t="n">
+      <c r="Y18" t="n">
         <v>5</v>
       </c>
-      <c r="Q18" t="n">
-        <v>0.02448029634417161</v>
-      </c>
-      <c r="R18" t="n">
-        <v>0.03303877311228397</v>
-      </c>
-      <c r="S18" t="n">
-        <v>1.66257235186108</v>
-      </c>
-      <c r="T18" t="n">
-        <v>0.5070071814842384</v>
-      </c>
-      <c r="U18" t="n">
-        <v>0.2449938638924828</v>
-      </c>
-      <c r="V18" t="n">
-        <v>0.1533631916714108</v>
-      </c>
-      <c r="W18" t="n">
-        <v>14.34085400030017</v>
-      </c>
-      <c r="X18" t="inlineStr">
-        <is>
-          <t>success</t>
-        </is>
-      </c>
-      <c r="Y18" t="inlineStr"/>
+      <c r="Z18" t="n">
+        <v>0.02409615005911813</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>0.03252101077839731</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>1.61258618294362</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>0.5095891037671815</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>0.306419275000533</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>0.1533095777784992</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>0.306419275000533</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>0.1533095777784992</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>16.55023870004516</v>
+      </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="AJ18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>architecture_tuning_esn_v1_20260329T153803Z</t>
+          <t>architecture_tuning_esn_v1_20260819T074659Z</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2442,54 +2752,69 @@
       </c>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" t="inlineStr"/>
+      <c r="P19" t="inlineStr"/>
+      <c r="Q19" t="inlineStr"/>
+      <c r="R19" t="inlineStr"/>
+      <c r="S19" t="inlineStr"/>
+      <c r="T19" t="inlineStr"/>
+      <c r="U19" t="inlineStr"/>
+      <c r="V19" t="inlineStr">
         <is>
           <t>{"compare_group_id": "esn_grp_002", "model_params": {"chaotic_spectral_radius": 1.25, "input_scale": 0.1, "leak_rate": 0.8, "n_reservoir": 96, "ridge_alpha": 0.0001, "seed": 2026, "spectral_radius": 0.95}, "runtime_params": {}}</t>
         </is>
       </c>
-      <c r="N19" t="inlineStr">
+      <c r="W19" t="inlineStr">
         <is>
           <t>{'model_params': {'n_reservoir': 96, 'spectral_radius': 0.95, 'chaotic_spectral_radius': 1.25, 'input_scale': 0.1, 'leak_rate': 0.8, 'ridge_alpha': 0.0001, 'seed': 2026}, 'runtime_params': {}, 'compare_group_id': 'esn_grp_002'}</t>
         </is>
       </c>
-      <c r="O19" t="n">
+      <c r="X19" t="n">
         <v>12</v>
       </c>
-      <c r="P19" t="n">
+      <c r="Y19" t="n">
         <v>20</v>
       </c>
-      <c r="Q19" t="n">
-        <v>0.05003216624556578</v>
-      </c>
-      <c r="R19" t="n">
-        <v>0.06728686751557349</v>
-      </c>
-      <c r="S19" t="n">
-        <v>3.382112977789939</v>
-      </c>
-      <c r="T19" t="n">
-        <v>0.5085186234446596</v>
-      </c>
-      <c r="U19" t="n">
-        <v>0.1228824500123867</v>
-      </c>
-      <c r="V19" t="n">
-        <v>0.07651925277766876</v>
-      </c>
-      <c r="W19" t="n">
-        <v>7.178461300441995</v>
-      </c>
-      <c r="X19" t="inlineStr">
-        <is>
-          <t>success</t>
-        </is>
-      </c>
-      <c r="Y19" t="inlineStr"/>
+      <c r="Z19" t="n">
+        <v>0.04857259972828862</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>0.06383819358061278</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>3.239073582853348</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>0.5128989198143334</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>0.15118385555373</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>0.07628512222274568</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>0.15118385555373</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>0.07628512222274568</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>8.188883199953125</v>
+      </c>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="AJ19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>architecture_tuning_esn_v1_20260329T153803Z</t>
+          <t>architecture_tuning_esn_v1_20260819T074659Z</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2527,54 +2852,69 @@
       </c>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="O20" t="inlineStr"/>
+      <c r="P20" t="inlineStr"/>
+      <c r="Q20" t="inlineStr"/>
+      <c r="R20" t="inlineStr"/>
+      <c r="S20" t="inlineStr"/>
+      <c r="T20" t="inlineStr"/>
+      <c r="U20" t="inlineStr"/>
+      <c r="V20" t="inlineStr">
         <is>
           <t>{"compare_group_id": "esn_grp_003", "model_params": {"chaotic_spectral_radius": 1.3, "input_scale": 0.08, "leak_rate": 0.7, "n_reservoir": 128, "ridge_alpha": 0.0005, "seed": 2026, "spectral_radius": 0.98}, "runtime_params": {}}</t>
         </is>
       </c>
-      <c r="N20" t="inlineStr">
+      <c r="W20" t="inlineStr">
         <is>
           <t>{'model_params': {'n_reservoir': 128, 'spectral_radius': 0.98, 'chaotic_spectral_radius': 1.3, 'input_scale': 0.08, 'leak_rate': 0.7, 'ridge_alpha': 0.0005, 'seed': 2026}, 'runtime_params': {}, 'compare_group_id': 'esn_grp_003'}</t>
         </is>
       </c>
-      <c r="O20" t="n">
+      <c r="X20" t="n">
         <v>12</v>
       </c>
-      <c r="P20" t="n">
+      <c r="Y20" t="n">
         <v>1</v>
       </c>
-      <c r="Q20" t="n">
-        <v>0.01228276575796864</v>
-      </c>
-      <c r="R20" t="n">
-        <v>0.01712374689667777</v>
-      </c>
-      <c r="S20" t="n">
-        <v>0.8060863918591687</v>
-      </c>
-      <c r="T20" t="n">
-        <v>0.4980924749643045</v>
-      </c>
-      <c r="U20" t="n">
-        <v>0.5773372555591374</v>
-      </c>
-      <c r="V20" t="n">
-        <v>0.3593873638827871</v>
-      </c>
-      <c r="W20" t="n">
-        <v>33.72208629990928</v>
-      </c>
-      <c r="X20" t="inlineStr">
-        <is>
-          <t>success</t>
-        </is>
-      </c>
-      <c r="Y20" t="inlineStr"/>
+      <c r="Z20" t="n">
+        <v>0.01181863895057717</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>0.01641847499296645</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>0.7766648674444675</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>0.492135760503269</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>0.7210298972224538</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>0.3572559388881523</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>0.7210298972224538</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>0.3572559388881523</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>38.81829009998182</v>
+      </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="AJ20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>architecture_tuning_esn_v1_20260329T153803Z</t>
+          <t>architecture_tuning_esn_v1_20260819T074659Z</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2612,54 +2952,69 @@
       </c>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="O21" t="inlineStr"/>
+      <c r="P21" t="inlineStr"/>
+      <c r="Q21" t="inlineStr"/>
+      <c r="R21" t="inlineStr"/>
+      <c r="S21" t="inlineStr"/>
+      <c r="T21" t="inlineStr"/>
+      <c r="U21" t="inlineStr"/>
+      <c r="V21" t="inlineStr">
         <is>
           <t>{"compare_group_id": "esn_grp_003", "model_params": {"chaotic_spectral_radius": 1.3, "input_scale": 0.08, "leak_rate": 0.7, "n_reservoir": 128, "ridge_alpha": 0.0005, "seed": 2026, "spectral_radius": 0.98}, "runtime_params": {}}</t>
         </is>
       </c>
-      <c r="N21" t="inlineStr">
+      <c r="W21" t="inlineStr">
         <is>
           <t>{'model_params': {'n_reservoir': 128, 'spectral_radius': 0.98, 'chaotic_spectral_radius': 1.3, 'input_scale': 0.08, 'leak_rate': 0.7, 'ridge_alpha': 0.0005, 'seed': 2026}, 'runtime_params': {}, 'compare_group_id': 'esn_grp_003'}</t>
         </is>
       </c>
-      <c r="O21" t="n">
+      <c r="X21" t="n">
         <v>12</v>
       </c>
-      <c r="P21" t="n">
+      <c r="Y21" t="n">
         <v>5</v>
       </c>
-      <c r="Q21" t="n">
-        <v>0.0247903115117102</v>
-      </c>
-      <c r="R21" t="n">
-        <v>0.03385488314017872</v>
-      </c>
-      <c r="S21" t="n">
-        <v>1.664331482706824</v>
-      </c>
-      <c r="T21" t="n">
-        <v>0.5158051480422144</v>
-      </c>
-      <c r="U21" t="n">
-        <v>0.2922291972208768</v>
-      </c>
-      <c r="V21" t="n">
-        <v>0.1816076861222326</v>
-      </c>
-      <c r="W21" t="n">
-        <v>17.05812780035194</v>
-      </c>
-      <c r="X21" t="inlineStr">
-        <is>
-          <t>success</t>
-        </is>
-      </c>
-      <c r="Y21" t="inlineStr"/>
+      <c r="Z21" t="n">
+        <v>0.02496988221433108</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>0.03457435954347253</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>1.662356770084173</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>0.5155655140995314</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>0.3646719027779505</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>0.1806538361112568</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>0.3646719027779505</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>0.1806538361112568</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>19.63172660001146</v>
+      </c>
+      <c r="AI21" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="AJ21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>architecture_tuning_esn_v1_20260329T153803Z</t>
+          <t>architecture_tuning_esn_v1_20260819T074659Z</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2697,54 +3052,69 @@
       </c>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="O22" t="inlineStr"/>
+      <c r="P22" t="inlineStr"/>
+      <c r="Q22" t="inlineStr"/>
+      <c r="R22" t="inlineStr"/>
+      <c r="S22" t="inlineStr"/>
+      <c r="T22" t="inlineStr"/>
+      <c r="U22" t="inlineStr"/>
+      <c r="V22" t="inlineStr">
         <is>
           <t>{"compare_group_id": "esn_grp_003", "model_params": {"chaotic_spectral_radius": 1.3, "input_scale": 0.08, "leak_rate": 0.7, "n_reservoir": 128, "ridge_alpha": 0.0005, "seed": 2026, "spectral_radius": 0.98}, "runtime_params": {}}</t>
         </is>
       </c>
-      <c r="N22" t="inlineStr">
+      <c r="W22" t="inlineStr">
         <is>
           <t>{'model_params': {'n_reservoir': 128, 'spectral_radius': 0.98, 'chaotic_spectral_radius': 1.3, 'input_scale': 0.08, 'leak_rate': 0.7, 'ridge_alpha': 0.0005, 'seed': 2026}, 'runtime_params': {}, 'compare_group_id': 'esn_grp_003'}</t>
         </is>
       </c>
-      <c r="O22" t="n">
+      <c r="X22" t="n">
         <v>12</v>
       </c>
-      <c r="P22" t="n">
+      <c r="Y22" t="n">
         <v>20</v>
       </c>
-      <c r="Q22" t="n">
-        <v>0.04753378675828981</v>
-      </c>
-      <c r="R22" t="n">
-        <v>0.0613365172320566</v>
-      </c>
-      <c r="S22" t="n">
-        <v>3.176695087997378</v>
-      </c>
-      <c r="T22" t="n">
-        <v>0.5008160627354807</v>
-      </c>
-      <c r="U22" t="n">
-        <v>0.1464355250096155</v>
-      </c>
-      <c r="V22" t="n">
-        <v>0.09128993333110379</v>
-      </c>
-      <c r="W22" t="n">
-        <v>8.558116500265896</v>
-      </c>
-      <c r="X22" t="inlineStr">
-        <is>
-          <t>success</t>
-        </is>
-      </c>
-      <c r="Y22" t="inlineStr"/>
+      <c r="Z22" t="n">
+        <v>0.04702765687279834</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>0.06090067397102622</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>3.116190669808164</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>0.5192840357813747</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>0.1841552027803522</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>0.09077436111086473</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>0.1841552027803522</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>0.09077436111086473</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>9.897464300083811</v>
+      </c>
+      <c r="AI22" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="AJ22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>architecture_tuning_esn_v1_20260329T153803Z</t>
+          <t>architecture_tuning_esn_v1_20260819T074659Z</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2782,54 +3152,69 @@
       </c>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="O23" t="inlineStr"/>
+      <c r="P23" t="inlineStr"/>
+      <c r="Q23" t="inlineStr"/>
+      <c r="R23" t="inlineStr"/>
+      <c r="S23" t="inlineStr"/>
+      <c r="T23" t="inlineStr"/>
+      <c r="U23" t="inlineStr"/>
+      <c r="V23" t="inlineStr">
         <is>
           <t>{"compare_group_id": "esn_grp_004", "model_params": {"chaotic_spectral_radius": 1.22, "input_scale": 0.12, "leak_rate": 0.9, "n_reservoir": 160, "ridge_alpha": 0.001, "seed": 2026, "spectral_radius": 0.92}, "runtime_params": {}}</t>
         </is>
       </c>
-      <c r="N23" t="inlineStr">
+      <c r="W23" t="inlineStr">
         <is>
           <t>{'model_params': {'n_reservoir': 160, 'spectral_radius': 0.92, 'chaotic_spectral_radius': 1.22, 'input_scale': 0.12, 'leak_rate': 0.9, 'ridge_alpha': 0.001, 'seed': 2026}, 'runtime_params': {}, 'compare_group_id': 'esn_grp_004'}</t>
         </is>
       </c>
-      <c r="O23" t="n">
+      <c r="X23" t="n">
         <v>12</v>
       </c>
-      <c r="P23" t="n">
+      <c r="Y23" t="n">
         <v>1</v>
       </c>
-      <c r="Q23" t="n">
-        <v>0.01173511768353693</v>
-      </c>
-      <c r="R23" t="n">
-        <v>0.01620455308007837</v>
-      </c>
-      <c r="S23" t="n">
-        <v>0.7727823461212906</v>
-      </c>
-      <c r="T23" t="n">
-        <v>0.4952180436518327</v>
-      </c>
-      <c r="U23" t="n">
-        <v>0.6685817138867504</v>
-      </c>
-      <c r="V23" t="n">
-        <v>0.415418097231951</v>
-      </c>
-      <c r="W23" t="n">
-        <v>39.02399320027325</v>
-      </c>
-      <c r="X23" t="inlineStr">
-        <is>
-          <t>success</t>
-        </is>
-      </c>
-      <c r="Y23" t="inlineStr"/>
+      <c r="Z23" t="n">
+        <v>0.01149276160761661</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>0.01584216330773356</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>0.7553368331132946</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>0.4919421186141159</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>0.8399394416669059</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>0.4186809833336156</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>0.8399394416669059</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>0.4186809833336156</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>45.31033530001878</v>
+      </c>
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="AJ23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>architecture_tuning_esn_v1_20260329T153803Z</t>
+          <t>architecture_tuning_esn_v1_20260819T074659Z</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2867,54 +3252,69 @@
       </c>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="O24" t="inlineStr"/>
+      <c r="P24" t="inlineStr"/>
+      <c r="Q24" t="inlineStr"/>
+      <c r="R24" t="inlineStr"/>
+      <c r="S24" t="inlineStr"/>
+      <c r="T24" t="inlineStr"/>
+      <c r="U24" t="inlineStr"/>
+      <c r="V24" t="inlineStr">
         <is>
           <t>{"compare_group_id": "esn_grp_004", "model_params": {"chaotic_spectral_radius": 1.22, "input_scale": 0.12, "leak_rate": 0.9, "n_reservoir": 160, "ridge_alpha": 0.001, "seed": 2026, "spectral_radius": 0.92}, "runtime_params": {}}</t>
         </is>
       </c>
-      <c r="N24" t="inlineStr">
+      <c r="W24" t="inlineStr">
         <is>
           <t>{'model_params': {'n_reservoir': 160, 'spectral_radius': 0.92, 'chaotic_spectral_radius': 1.22, 'input_scale': 0.12, 'leak_rate': 0.9, 'ridge_alpha': 0.001, 'seed': 2026}, 'runtime_params': {}, 'compare_group_id': 'esn_grp_004'}</t>
         </is>
       </c>
-      <c r="O24" t="n">
+      <c r="X24" t="n">
         <v>12</v>
       </c>
-      <c r="P24" t="n">
+      <c r="Y24" t="n">
         <v>5</v>
       </c>
-      <c r="Q24" t="n">
-        <v>0.02544268153310842</v>
-      </c>
-      <c r="R24" t="n">
-        <v>0.0346726405740809</v>
-      </c>
-      <c r="S24" t="n">
-        <v>1.699534764398839</v>
-      </c>
-      <c r="T24" t="n">
-        <v>0.5114988015253513</v>
-      </c>
-      <c r="U24" t="n">
-        <v>0.3372026611177717</v>
-      </c>
-      <c r="V24" t="n">
-        <v>0.2099167972175766</v>
-      </c>
-      <c r="W24" t="n">
-        <v>19.69630050007254</v>
-      </c>
-      <c r="X24" t="inlineStr">
-        <is>
-          <t>success</t>
-        </is>
-      </c>
-      <c r="Y24" t="inlineStr"/>
+      <c r="Z24" t="n">
+        <v>0.02498120703078086</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>0.0338835178061632</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>1.653567809792152</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>0.5166160055296662</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>0.4305418861101013</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>0.2121204000015698</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>0.4305418861101013</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>0.2121204000015698</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>23.13584230002016</v>
+      </c>
+      <c r="AI24" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="AJ24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>architecture_tuning_esn_v1_20260329T153803Z</t>
+          <t>architecture_tuning_esn_v1_20260819T074659Z</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2952,54 +3352,69 @@
       </c>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="O25" t="inlineStr"/>
+      <c r="P25" t="inlineStr"/>
+      <c r="Q25" t="inlineStr"/>
+      <c r="R25" t="inlineStr"/>
+      <c r="S25" t="inlineStr"/>
+      <c r="T25" t="inlineStr"/>
+      <c r="U25" t="inlineStr"/>
+      <c r="V25" t="inlineStr">
         <is>
           <t>{"compare_group_id": "esn_grp_004", "model_params": {"chaotic_spectral_radius": 1.22, "input_scale": 0.12, "leak_rate": 0.9, "n_reservoir": 160, "ridge_alpha": 0.001, "seed": 2026, "spectral_radius": 0.92}, "runtime_params": {}}</t>
         </is>
       </c>
-      <c r="N25" t="inlineStr">
+      <c r="W25" t="inlineStr">
         <is>
           <t>{'model_params': {'n_reservoir': 160, 'spectral_radius': 0.92, 'chaotic_spectral_radius': 1.22, 'input_scale': 0.12, 'leak_rate': 0.9, 'ridge_alpha': 0.001, 'seed': 2026}, 'runtime_params': {}, 'compare_group_id': 'esn_grp_004'}</t>
         </is>
       </c>
-      <c r="O25" t="n">
+      <c r="X25" t="n">
         <v>12</v>
       </c>
-      <c r="P25" t="n">
+      <c r="Y25" t="n">
         <v>20</v>
       </c>
-      <c r="Q25" t="n">
-        <v>0.04764911907732803</v>
-      </c>
-      <c r="R25" t="n">
-        <v>0.06143807819686486</v>
-      </c>
-      <c r="S25" t="n">
-        <v>3.180126727042346</v>
-      </c>
-      <c r="T25" t="n">
-        <v>0.5019617008975968</v>
-      </c>
-      <c r="U25" t="n">
-        <v>0.1701978722121567</v>
-      </c>
-      <c r="V25" t="n">
-        <v>0.1051318916724995</v>
-      </c>
-      <c r="W25" t="n">
-        <v>9.911871499847621</v>
-      </c>
-      <c r="X25" t="inlineStr">
-        <is>
-          <t>success</t>
-        </is>
-      </c>
-      <c r="Y25" t="inlineStr"/>
+      <c r="Z25" t="n">
+        <v>0.04734201020209549</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>0.06140136729174572</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>3.133902060173185</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>0.5191353152438783</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>0.2128047277781459</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>0.1043259333342171</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>0.2128047277781459</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>0.1043259333342171</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>11.41670380004507</v>
+      </c>
+      <c r="AI25" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="AJ25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>architecture_tuning_esn_v1_20260329T153803Z</t>
+          <t>architecture_tuning_esn_v1_20260819T074659Z</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3039,54 +3454,69 @@
       <c r="L26" t="n">
         <v>0.95</v>
       </c>
-      <c r="M26" t="inlineStr">
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+      <c r="O26" t="inlineStr"/>
+      <c r="P26" t="inlineStr"/>
+      <c r="Q26" t="inlineStr"/>
+      <c r="R26" t="inlineStr"/>
+      <c r="S26" t="inlineStr"/>
+      <c r="T26" t="inlineStr"/>
+      <c r="U26" t="inlineStr"/>
+      <c r="V26" t="inlineStr">
         <is>
           <t>{"compare_group_id": "esn_grp_001", "model_params": {"g_end": 0.95, "g_start": 1.25, "input_scale": 0.1, "leak_rate": 1.0, "n_reservoir": 64, "ridge_alpha": 0.0001, "seed": 2026, "spectral_radius": 0.9}, "runtime_params": {}}</t>
         </is>
       </c>
-      <c r="N26" t="inlineStr">
+      <c r="W26" t="inlineStr">
         <is>
           <t>{'model_params': {'n_reservoir': 64, 'spectral_radius': 0.9, 'input_scale': 0.1, 'leak_rate': 1.0, 'ridge_alpha': 0.0001, 'g_start': 1.25, 'g_end': 0.95, 'seed': 2026}, 'runtime_params': {}, 'compare_group_id': 'esn_grp_001'}</t>
         </is>
       </c>
-      <c r="O26" t="n">
+      <c r="X26" t="n">
         <v>12</v>
       </c>
-      <c r="P26" t="n">
+      <c r="Y26" t="n">
         <v>1</v>
       </c>
-      <c r="Q26" t="n">
-        <v>0.01039239073857835</v>
-      </c>
-      <c r="R26" t="n">
-        <v>0.01435703603003999</v>
-      </c>
-      <c r="S26" t="n">
-        <v>0.6823097855474165</v>
-      </c>
-      <c r="T26" t="n">
-        <v>0.5054894164482692</v>
-      </c>
-      <c r="U26" t="n">
-        <v>0.53549203333225</v>
-      </c>
-      <c r="V26" t="n">
-        <v>0.3339243666689274</v>
-      </c>
-      <c r="W26" t="n">
-        <v>31.29899040004238</v>
-      </c>
-      <c r="X26" t="inlineStr">
-        <is>
-          <t>success</t>
-        </is>
-      </c>
-      <c r="Y26" t="inlineStr"/>
+      <c r="Z26" t="n">
+        <v>0.01039805345158544</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>0.01435359125034541</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>0.682842942266781</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>0.5020864006201495</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>0.6686506472227242</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>0.3329404361118375</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>0.6686506472227242</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>0.3329404361118375</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>36.05727900004422</v>
+      </c>
+      <c r="AI26" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="AJ26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>architecture_tuning_esn_v1_20260329T153803Z</t>
+          <t>architecture_tuning_esn_v1_20260819T074659Z</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3126,54 +3556,69 @@
       <c r="L27" t="n">
         <v>0.95</v>
       </c>
-      <c r="M27" t="inlineStr">
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
+      <c r="O27" t="inlineStr"/>
+      <c r="P27" t="inlineStr"/>
+      <c r="Q27" t="inlineStr"/>
+      <c r="R27" t="inlineStr"/>
+      <c r="S27" t="inlineStr"/>
+      <c r="T27" t="inlineStr"/>
+      <c r="U27" t="inlineStr"/>
+      <c r="V27" t="inlineStr">
         <is>
           <t>{"compare_group_id": "esn_grp_001", "model_params": {"g_end": 0.95, "g_start": 1.25, "input_scale": 0.1, "leak_rate": 1.0, "n_reservoir": 64, "ridge_alpha": 0.0001, "seed": 2026, "spectral_radius": 0.9}, "runtime_params": {}}</t>
         </is>
       </c>
-      <c r="N27" t="inlineStr">
+      <c r="W27" t="inlineStr">
         <is>
           <t>{'model_params': {'n_reservoir': 64, 'spectral_radius': 0.9, 'input_scale': 0.1, 'leak_rate': 1.0, 'ridge_alpha': 0.0001, 'g_start': 1.25, 'g_end': 0.95, 'seed': 2026}, 'runtime_params': {}, 'compare_group_id': 'esn_grp_001'}</t>
         </is>
       </c>
-      <c r="O27" t="n">
+      <c r="X27" t="n">
         <v>12</v>
       </c>
-      <c r="P27" t="n">
+      <c r="Y27" t="n">
         <v>5</v>
       </c>
-      <c r="Q27" t="n">
-        <v>0.02340737598713888</v>
-      </c>
-      <c r="R27" t="n">
-        <v>0.03152207712618327</v>
-      </c>
-      <c r="S27" t="n">
-        <v>1.574202895064655</v>
-      </c>
-      <c r="T27" t="n">
-        <v>0.5099978290644331</v>
-      </c>
-      <c r="U27" t="n">
-        <v>0.2723160888741</v>
-      </c>
-      <c r="V27" t="n">
-        <v>0.1703108583460562</v>
-      </c>
-      <c r="W27" t="n">
-        <v>15.93457009992562</v>
-      </c>
-      <c r="X27" t="inlineStr">
-        <is>
-          <t>success</t>
-        </is>
-      </c>
-      <c r="Y27" t="inlineStr"/>
+      <c r="Z27" t="n">
+        <v>0.02319330673262766</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>0.03127596679455818</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>1.540646596991733</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>0.5153734383667447</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>0.3385760972220548</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>0.1695943305559113</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>0.3385760972220548</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>0.1695943305559113</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>18.29413540000678</v>
+      </c>
+      <c r="AI27" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="AJ27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>architecture_tuning_esn_v1_20260329T153803Z</t>
+          <t>architecture_tuning_esn_v1_20260819T074659Z</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3213,54 +3658,69 @@
       <c r="L28" t="n">
         <v>0.95</v>
       </c>
-      <c r="M28" t="inlineStr">
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
+      <c r="O28" t="inlineStr"/>
+      <c r="P28" t="inlineStr"/>
+      <c r="Q28" t="inlineStr"/>
+      <c r="R28" t="inlineStr"/>
+      <c r="S28" t="inlineStr"/>
+      <c r="T28" t="inlineStr"/>
+      <c r="U28" t="inlineStr"/>
+      <c r="V28" t="inlineStr">
         <is>
           <t>{"compare_group_id": "esn_grp_001", "model_params": {"g_end": 0.95, "g_start": 1.25, "input_scale": 0.1, "leak_rate": 1.0, "n_reservoir": 64, "ridge_alpha": 0.0001, "seed": 2026, "spectral_radius": 0.9}, "runtime_params": {}}</t>
         </is>
       </c>
-      <c r="N28" t="inlineStr">
+      <c r="W28" t="inlineStr">
         <is>
           <t>{'model_params': {'n_reservoir': 64, 'spectral_radius': 0.9, 'input_scale': 0.1, 'leak_rate': 1.0, 'ridge_alpha': 0.0001, 'g_start': 1.25, 'g_end': 0.95, 'seed': 2026}, 'runtime_params': {}, 'compare_group_id': 'esn_grp_001'}</t>
         </is>
       </c>
-      <c r="O28" t="n">
+      <c r="X28" t="n">
         <v>12</v>
       </c>
-      <c r="P28" t="n">
+      <c r="Y28" t="n">
         <v>20</v>
       </c>
-      <c r="Q28" t="n">
-        <v>0.04764358963206822</v>
-      </c>
-      <c r="R28" t="n">
-        <v>0.06153319807607405</v>
-      </c>
-      <c r="S28" t="n">
-        <v>3.187049894276723</v>
-      </c>
-      <c r="T28" t="n">
-        <v>0.4968998989018674</v>
-      </c>
-      <c r="U28" t="n">
-        <v>0.1372384083353811</v>
-      </c>
-      <c r="V28" t="n">
-        <v>0.08573396110700238</v>
-      </c>
-      <c r="W28" t="n">
-        <v>8.027005299925804</v>
-      </c>
-      <c r="X28" t="inlineStr">
-        <is>
-          <t>success</t>
-        </is>
-      </c>
-      <c r="Y28" t="inlineStr"/>
+      <c r="Z28" t="n">
+        <v>0.04699795988071519</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>0.06081050625940255</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>3.112391186133248</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>0.5159199748944551</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>0.1680047277780735</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>0.08509095000004485</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>0.1680047277780735</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>0.08509095000004485</v>
+      </c>
+      <c r="AH28" t="n">
+        <v>9.11144440001226</v>
+      </c>
+      <c r="AI28" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="AJ28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>architecture_tuning_esn_v1_20260329T153803Z</t>
+          <t>architecture_tuning_esn_v1_20260819T074659Z</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3300,54 +3760,69 @@
       <c r="L29" t="n">
         <v>0.95</v>
       </c>
-      <c r="M29" t="inlineStr">
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
+      <c r="O29" t="inlineStr"/>
+      <c r="P29" t="inlineStr"/>
+      <c r="Q29" t="inlineStr"/>
+      <c r="R29" t="inlineStr"/>
+      <c r="S29" t="inlineStr"/>
+      <c r="T29" t="inlineStr"/>
+      <c r="U29" t="inlineStr"/>
+      <c r="V29" t="inlineStr">
         <is>
           <t>{"compare_group_id": "esn_grp_002", "model_params": {"g_end": 0.95, "g_start": 1.3, "input_scale": 0.1, "leak_rate": 0.8, "n_reservoir": 96, "ridge_alpha": 0.0001, "seed": 2026, "spectral_radius": 0.95}, "runtime_params": {}}</t>
         </is>
       </c>
-      <c r="N29" t="inlineStr">
+      <c r="W29" t="inlineStr">
         <is>
           <t>{'model_params': {'n_reservoir': 96, 'spectral_radius': 0.95, 'input_scale': 0.1, 'leak_rate': 0.8, 'ridge_alpha': 0.0001, 'g_start': 1.3, 'g_end': 0.95, 'seed': 2026}, 'runtime_params': {}, 'compare_group_id': 'esn_grp_002'}</t>
         </is>
       </c>
-      <c r="O29" t="n">
+      <c r="X29" t="n">
         <v>12</v>
       </c>
-      <c r="P29" t="n">
+      <c r="Y29" t="n">
         <v>1</v>
       </c>
-      <c r="Q29" t="n">
-        <v>0.01036084894920913</v>
-      </c>
-      <c r="R29" t="n">
-        <v>0.01432430920963849</v>
-      </c>
-      <c r="S29" t="n">
-        <v>0.6794599394499302</v>
-      </c>
-      <c r="T29" t="n">
-        <v>0.5009191533421151</v>
-      </c>
-      <c r="U29" t="n">
-        <v>0.584345080559918</v>
-      </c>
-      <c r="V29" t="n">
-        <v>0.3666639833342439</v>
-      </c>
-      <c r="W29" t="n">
-        <v>34.23632630018983</v>
-      </c>
-      <c r="X29" t="inlineStr">
-        <is>
-          <t>success</t>
-        </is>
-      </c>
-      <c r="Y29" t="inlineStr"/>
+      <c r="Z29" t="n">
+        <v>0.01035982351147461</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>0.01431681599139619</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>0.6796047078339283</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>0.5016218472485754</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>0.7282935416660621</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>0.3656154750012017</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>0.7282935416660621</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>0.3656154750012017</v>
+      </c>
+      <c r="AH29" t="n">
+        <v>39.38072460002149</v>
+      </c>
+      <c r="AI29" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="AJ29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>architecture_tuning_esn_v1_20260329T153803Z</t>
+          <t>architecture_tuning_esn_v1_20260819T074659Z</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3387,54 +3862,69 @@
       <c r="L30" t="n">
         <v>0.95</v>
       </c>
-      <c r="M30" t="inlineStr">
+      <c r="M30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
+      <c r="O30" t="inlineStr"/>
+      <c r="P30" t="inlineStr"/>
+      <c r="Q30" t="inlineStr"/>
+      <c r="R30" t="inlineStr"/>
+      <c r="S30" t="inlineStr"/>
+      <c r="T30" t="inlineStr"/>
+      <c r="U30" t="inlineStr"/>
+      <c r="V30" t="inlineStr">
         <is>
           <t>{"compare_group_id": "esn_grp_002", "model_params": {"g_end": 0.95, "g_start": 1.3, "input_scale": 0.1, "leak_rate": 0.8, "n_reservoir": 96, "ridge_alpha": 0.0001, "seed": 2026, "spectral_radius": 0.95}, "runtime_params": {}}</t>
         </is>
       </c>
-      <c r="N30" t="inlineStr">
+      <c r="W30" t="inlineStr">
         <is>
           <t>{'model_params': {'n_reservoir': 96, 'spectral_radius': 0.95, 'input_scale': 0.1, 'leak_rate': 0.8, 'ridge_alpha': 0.0001, 'g_start': 1.3, 'g_end': 0.95, 'seed': 2026}, 'runtime_params': {}, 'compare_group_id': 'esn_grp_002'}</t>
         </is>
       </c>
-      <c r="O30" t="n">
+      <c r="X30" t="n">
         <v>12</v>
       </c>
-      <c r="P30" t="n">
+      <c r="Y30" t="n">
         <v>5</v>
       </c>
-      <c r="Q30" t="n">
-        <v>0.02333578608268773</v>
-      </c>
-      <c r="R30" t="n">
-        <v>0.031449819400724</v>
-      </c>
-      <c r="S30" t="n">
-        <v>1.564014656433759</v>
-      </c>
-      <c r="T30" t="n">
-        <v>0.5127796974974874</v>
-      </c>
-      <c r="U30" t="n">
-        <v>0.2981677027904273</v>
-      </c>
-      <c r="V30" t="n">
-        <v>0.1864609111152175</v>
-      </c>
-      <c r="W30" t="n">
-        <v>17.44663010060322</v>
-      </c>
-      <c r="X30" t="inlineStr">
-        <is>
-          <t>success</t>
-        </is>
-      </c>
-      <c r="Y30" t="inlineStr"/>
+      <c r="Z30" t="n">
+        <v>0.02317910650167047</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>0.03126585328316814</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>1.539271102543768</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>0.5197676959555365</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>0.3700171194448356</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>0.1853652888878261</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>0.3700171194448356</v>
+      </c>
+      <c r="AG30" t="n">
+        <v>0.1853652888878261</v>
+      </c>
+      <c r="AH30" t="n">
+        <v>19.99376669997582</v>
+      </c>
+      <c r="AI30" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="AJ30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>architecture_tuning_esn_v1_20260329T153803Z</t>
+          <t>architecture_tuning_esn_v1_20260819T074659Z</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3474,54 +3964,69 @@
       <c r="L31" t="n">
         <v>0.95</v>
       </c>
-      <c r="M31" t="inlineStr">
+      <c r="M31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
+      <c r="O31" t="inlineStr"/>
+      <c r="P31" t="inlineStr"/>
+      <c r="Q31" t="inlineStr"/>
+      <c r="R31" t="inlineStr"/>
+      <c r="S31" t="inlineStr"/>
+      <c r="T31" t="inlineStr"/>
+      <c r="U31" t="inlineStr"/>
+      <c r="V31" t="inlineStr">
         <is>
           <t>{"compare_group_id": "esn_grp_002", "model_params": {"g_end": 0.95, "g_start": 1.3, "input_scale": 0.1, "leak_rate": 0.8, "n_reservoir": 96, "ridge_alpha": 0.0001, "seed": 2026, "spectral_radius": 0.95}, "runtime_params": {}}</t>
         </is>
       </c>
-      <c r="N31" t="inlineStr">
+      <c r="W31" t="inlineStr">
         <is>
           <t>{'model_params': {'n_reservoir': 96, 'spectral_radius': 0.95, 'input_scale': 0.1, 'leak_rate': 0.8, 'ridge_alpha': 0.0001, 'g_start': 1.3, 'g_end': 0.95, 'seed': 2026}, 'runtime_params': {}, 'compare_group_id': 'esn_grp_002'}</t>
         </is>
       </c>
-      <c r="O31" t="n">
+      <c r="X31" t="n">
         <v>12</v>
       </c>
-      <c r="P31" t="n">
+      <c r="Y31" t="n">
         <v>20</v>
       </c>
-      <c r="Q31" t="n">
-        <v>0.04759312950856324</v>
-      </c>
-      <c r="R31" t="n">
-        <v>0.06147920160763922</v>
-      </c>
-      <c r="S31" t="n">
-        <v>3.186062202025597</v>
-      </c>
-      <c r="T31" t="n">
-        <v>0.4970098605210711</v>
-      </c>
-      <c r="U31" t="n">
-        <v>0.1501619861066704</v>
-      </c>
-      <c r="V31" t="n">
-        <v>0.09320005834645902</v>
-      </c>
-      <c r="W31" t="n">
-        <v>8.761033600312658</v>
-      </c>
-      <c r="X31" t="inlineStr">
-        <is>
-          <t>success</t>
-        </is>
-      </c>
-      <c r="Y31" t="inlineStr"/>
+      <c r="Z31" t="n">
+        <v>0.04693362131005851</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>0.0607416612846192</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>3.110853330250367</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>0.5210938400520722</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>0.1842380222228207</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>0.09385663333361866</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>0.1842380222228207</v>
+      </c>
+      <c r="AG31" t="n">
+        <v>0.09385663333361866</v>
+      </c>
+      <c r="AH31" t="n">
+        <v>10.01140760003182</v>
+      </c>
+      <c r="AI31" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="AJ31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>architecture_tuning_esn_v1_20260329T153803Z</t>
+          <t>architecture_tuning_esn_v1_20260819T074659Z</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3561,54 +4066,69 @@
       <c r="L32" t="n">
         <v>0.95</v>
       </c>
-      <c r="M32" t="inlineStr">
+      <c r="M32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
+      <c r="O32" t="inlineStr"/>
+      <c r="P32" t="inlineStr"/>
+      <c r="Q32" t="inlineStr"/>
+      <c r="R32" t="inlineStr"/>
+      <c r="S32" t="inlineStr"/>
+      <c r="T32" t="inlineStr"/>
+      <c r="U32" t="inlineStr"/>
+      <c r="V32" t="inlineStr">
         <is>
           <t>{"compare_group_id": "esn_grp_003", "model_params": {"g_end": 0.95, "g_start": 1.35, "input_scale": 0.08, "leak_rate": 0.7, "n_reservoir": 128, "ridge_alpha": 0.0005, "seed": 2026, "spectral_radius": 0.98}, "runtime_params": {}}</t>
         </is>
       </c>
-      <c r="N32" t="inlineStr">
+      <c r="W32" t="inlineStr">
         <is>
           <t>{'model_params': {'n_reservoir': 128, 'spectral_radius': 0.98, 'input_scale': 0.08, 'leak_rate': 0.7, 'ridge_alpha': 0.0005, 'g_start': 1.35, 'g_end': 0.95, 'seed': 2026}, 'runtime_params': {}, 'compare_group_id': 'esn_grp_003'}</t>
         </is>
       </c>
-      <c r="O32" t="n">
+      <c r="X32" t="n">
         <v>12</v>
       </c>
-      <c r="P32" t="n">
+      <c r="Y32" t="n">
         <v>1</v>
       </c>
-      <c r="Q32" t="n">
-        <v>0.01038534467211033</v>
-      </c>
-      <c r="R32" t="n">
-        <v>0.01432024681459104</v>
-      </c>
-      <c r="S32" t="n">
-        <v>0.6820023404138263</v>
-      </c>
-      <c r="T32" t="n">
-        <v>0.503699893742481</v>
-      </c>
-      <c r="U32" t="n">
-        <v>0.6894672555596721</v>
-      </c>
-      <c r="V32" t="n">
-        <v>0.4280105249910977</v>
-      </c>
-      <c r="W32" t="n">
-        <v>40.22920009982772</v>
-      </c>
-      <c r="X32" t="inlineStr">
-        <is>
-          <t>success</t>
-        </is>
-      </c>
-      <c r="Y32" t="inlineStr"/>
+      <c r="Z32" t="n">
+        <v>0.01037423045476002</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>0.01430735416076453</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>0.6807853998881336</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>0.5029534467196097</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>0.8564669472236548</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>0.4260028194471994</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>0.8564669472236548</v>
+      </c>
+      <c r="AG32" t="n">
+        <v>0.4260028194471994</v>
+      </c>
+      <c r="AH32" t="n">
+        <v>46.16891160015075</v>
+      </c>
+      <c r="AI32" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="AJ32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>architecture_tuning_esn_v1_20260329T153803Z</t>
+          <t>architecture_tuning_esn_v1_20260819T074659Z</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3648,54 +4168,69 @@
       <c r="L33" t="n">
         <v>0.95</v>
       </c>
-      <c r="M33" t="inlineStr">
+      <c r="M33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
+      <c r="O33" t="inlineStr"/>
+      <c r="P33" t="inlineStr"/>
+      <c r="Q33" t="inlineStr"/>
+      <c r="R33" t="inlineStr"/>
+      <c r="S33" t="inlineStr"/>
+      <c r="T33" t="inlineStr"/>
+      <c r="U33" t="inlineStr"/>
+      <c r="V33" t="inlineStr">
         <is>
           <t>{"compare_group_id": "esn_grp_003", "model_params": {"g_end": 0.95, "g_start": 1.35, "input_scale": 0.08, "leak_rate": 0.7, "n_reservoir": 128, "ridge_alpha": 0.0005, "seed": 2026, "spectral_radius": 0.98}, "runtime_params": {}}</t>
         </is>
       </c>
-      <c r="N33" t="inlineStr">
+      <c r="W33" t="inlineStr">
         <is>
           <t>{'model_params': {'n_reservoir': 128, 'spectral_radius': 0.98, 'input_scale': 0.08, 'leak_rate': 0.7, 'ridge_alpha': 0.0005, 'g_start': 1.35, 'g_end': 0.95, 'seed': 2026}, 'runtime_params': {}, 'compare_group_id': 'esn_grp_003'}</t>
         </is>
       </c>
-      <c r="O33" t="n">
+      <c r="X33" t="n">
         <v>12</v>
       </c>
-      <c r="P33" t="n">
+      <c r="Y33" t="n">
         <v>5</v>
       </c>
-      <c r="Q33" t="n">
-        <v>0.02339023900983392</v>
-      </c>
-      <c r="R33" t="n">
-        <v>0.0315029790451099</v>
-      </c>
-      <c r="S33" t="n">
-        <v>1.572929768442791</v>
-      </c>
-      <c r="T33" t="n">
-        <v>0.5122899792109157</v>
-      </c>
-      <c r="U33" t="n">
-        <v>0.3515669194425249</v>
-      </c>
-      <c r="V33" t="n">
-        <v>0.218529252781688</v>
-      </c>
-      <c r="W33" t="n">
-        <v>20.52346220007166</v>
-      </c>
-      <c r="X33" t="inlineStr">
-        <is>
-          <t>success</t>
-        </is>
-      </c>
-      <c r="Y33" t="inlineStr"/>
+      <c r="Z33" t="n">
+        <v>0.02318381659998701</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>0.03128515317490983</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>1.540024318072766</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>0.5153867822902943</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>0.4327314333337806</v>
+      </c>
+      <c r="AE33" t="n">
+        <v>0.2153785722225115</v>
+      </c>
+      <c r="AF33" t="n">
+        <v>0.4327314333337806</v>
+      </c>
+      <c r="AG33" t="n">
+        <v>0.2153785722225115</v>
+      </c>
+      <c r="AH33" t="n">
+        <v>23.33196020002651</v>
+      </c>
+      <c r="AI33" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="AJ33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>architecture_tuning_esn_v1_20260329T153803Z</t>
+          <t>architecture_tuning_esn_v1_20260819T074659Z</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3735,54 +4270,69 @@
       <c r="L34" t="n">
         <v>0.95</v>
       </c>
-      <c r="M34" t="inlineStr">
+      <c r="M34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
+      <c r="O34" t="inlineStr"/>
+      <c r="P34" t="inlineStr"/>
+      <c r="Q34" t="inlineStr"/>
+      <c r="R34" t="inlineStr"/>
+      <c r="S34" t="inlineStr"/>
+      <c r="T34" t="inlineStr"/>
+      <c r="U34" t="inlineStr"/>
+      <c r="V34" t="inlineStr">
         <is>
           <t>{"compare_group_id": "esn_grp_003", "model_params": {"g_end": 0.95, "g_start": 1.35, "input_scale": 0.08, "leak_rate": 0.7, "n_reservoir": 128, "ridge_alpha": 0.0005, "seed": 2026, "spectral_radius": 0.98}, "runtime_params": {}}</t>
         </is>
       </c>
-      <c r="N34" t="inlineStr">
+      <c r="W34" t="inlineStr">
         <is>
           <t>{'model_params': {'n_reservoir': 128, 'spectral_radius': 0.98, 'input_scale': 0.08, 'leak_rate': 0.7, 'ridge_alpha': 0.0005, 'g_start': 1.35, 'g_end': 0.95, 'seed': 2026}, 'runtime_params': {}, 'compare_group_id': 'esn_grp_003'}</t>
         </is>
       </c>
-      <c r="O34" t="n">
+      <c r="X34" t="n">
         <v>12</v>
       </c>
-      <c r="P34" t="n">
+      <c r="Y34" t="n">
         <v>20</v>
       </c>
-      <c r="Q34" t="n">
-        <v>0.04778486189622352</v>
-      </c>
-      <c r="R34" t="n">
-        <v>0.0615961838451452</v>
-      </c>
-      <c r="S34" t="n">
-        <v>3.191914039375044</v>
-      </c>
-      <c r="T34" t="n">
-        <v>0.4960823451414578</v>
-      </c>
-      <c r="U34" t="n">
-        <v>0.1763470444582506</v>
-      </c>
-      <c r="V34" t="n">
-        <v>0.1088208805433371</v>
-      </c>
-      <c r="W34" t="n">
-        <v>10.26604530005716</v>
-      </c>
-      <c r="X34" t="inlineStr">
-        <is>
-          <t>success</t>
-        </is>
-      </c>
-      <c r="Y34" t="inlineStr"/>
+      <c r="Z34" t="n">
+        <v>0.04726913975724174</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>0.06104962526401092</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>3.122151077860307</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>0.5171192423505391</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>0.2160806472226492</v>
+      </c>
+      <c r="AE34" t="n">
+        <v>0.1081289972236037</v>
+      </c>
+      <c r="AF34" t="n">
+        <v>0.2160806472226492</v>
+      </c>
+      <c r="AG34" t="n">
+        <v>0.1081289972236037</v>
+      </c>
+      <c r="AH34" t="n">
+        <v>11.67154720006511</v>
+      </c>
+      <c r="AI34" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="AJ34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>architecture_tuning_esn_v1_20260329T153803Z</t>
+          <t>architecture_tuning_esn_v1_20260819T074659Z</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3822,54 +4372,69 @@
       <c r="L35" t="n">
         <v>0.95</v>
       </c>
-      <c r="M35" t="inlineStr">
+      <c r="M35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
+      <c r="O35" t="inlineStr"/>
+      <c r="P35" t="inlineStr"/>
+      <c r="Q35" t="inlineStr"/>
+      <c r="R35" t="inlineStr"/>
+      <c r="S35" t="inlineStr"/>
+      <c r="T35" t="inlineStr"/>
+      <c r="U35" t="inlineStr"/>
+      <c r="V35" t="inlineStr">
         <is>
           <t>{"compare_group_id": "esn_grp_004", "model_params": {"g_end": 0.95, "g_start": 1.28, "input_scale": 0.12, "leak_rate": 0.9, "n_reservoir": 160, "ridge_alpha": 0.001, "seed": 2026, "spectral_radius": 0.92}, "runtime_params": {}}</t>
         </is>
       </c>
-      <c r="N35" t="inlineStr">
+      <c r="W35" t="inlineStr">
         <is>
           <t>{'model_params': {'n_reservoir': 160, 'spectral_radius': 0.92, 'input_scale': 0.12, 'leak_rate': 0.9, 'ridge_alpha': 0.001, 'g_start': 1.28, 'g_end': 0.95, 'seed': 2026}, 'runtime_params': {}, 'compare_group_id': 'esn_grp_004'}</t>
         </is>
       </c>
-      <c r="O35" t="n">
+      <c r="X35" t="n">
         <v>12</v>
       </c>
-      <c r="P35" t="n">
+      <c r="Y35" t="n">
         <v>1</v>
       </c>
-      <c r="Q35" t="n">
-        <v>0.01036038484005677</v>
-      </c>
-      <c r="R35" t="n">
-        <v>0.0143152218649881</v>
-      </c>
-      <c r="S35" t="n">
-        <v>0.6785631470407831</v>
-      </c>
-      <c r="T35" t="n">
-        <v>0.5026751090713998</v>
-      </c>
-      <c r="U35" t="n">
-        <v>0.7846242750011799</v>
-      </c>
-      <c r="V35" t="n">
-        <v>0.4891986444514865</v>
-      </c>
-      <c r="W35" t="n">
-        <v>45.85762510029599</v>
-      </c>
-      <c r="X35" t="inlineStr">
-        <is>
-          <t>success</t>
-        </is>
-      </c>
-      <c r="Y35" t="inlineStr"/>
+      <c r="Z35" t="n">
+        <v>0.01036178265425768</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>0.01431110940404351</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>0.6790134577608296</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>0.4999999915857551</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>0.9779223000009045</v>
+      </c>
+      <c r="AE35" t="n">
+        <v>0.4848442444437954</v>
+      </c>
+      <c r="AF35" t="n">
+        <v>0.9779223000009045</v>
+      </c>
+      <c r="AG35" t="n">
+        <v>0.4848442444437954</v>
+      </c>
+      <c r="AH35" t="n">
+        <v>52.6595956000092</v>
+      </c>
+      <c r="AI35" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="AJ35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>architecture_tuning_esn_v1_20260329T153803Z</t>
+          <t>architecture_tuning_esn_v1_20260819T074659Z</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3909,54 +4474,69 @@
       <c r="L36" t="n">
         <v>0.95</v>
       </c>
-      <c r="M36" t="inlineStr">
+      <c r="M36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
+      <c r="O36" t="inlineStr"/>
+      <c r="P36" t="inlineStr"/>
+      <c r="Q36" t="inlineStr"/>
+      <c r="R36" t="inlineStr"/>
+      <c r="S36" t="inlineStr"/>
+      <c r="T36" t="inlineStr"/>
+      <c r="U36" t="inlineStr"/>
+      <c r="V36" t="inlineStr">
         <is>
           <t>{"compare_group_id": "esn_grp_004", "model_params": {"g_end": 0.95, "g_start": 1.28, "input_scale": 0.12, "leak_rate": 0.9, "n_reservoir": 160, "ridge_alpha": 0.001, "seed": 2026, "spectral_radius": 0.92}, "runtime_params": {}}</t>
         </is>
       </c>
-      <c r="N36" t="inlineStr">
+      <c r="W36" t="inlineStr">
         <is>
           <t>{'model_params': {'n_reservoir': 160, 'spectral_radius': 0.92, 'input_scale': 0.12, 'leak_rate': 0.9, 'ridge_alpha': 0.001, 'g_start': 1.28, 'g_end': 0.95, 'seed': 2026}, 'runtime_params': {}, 'compare_group_id': 'esn_grp_004'}</t>
         </is>
       </c>
-      <c r="O36" t="n">
+      <c r="X36" t="n">
         <v>12</v>
       </c>
-      <c r="P36" t="n">
+      <c r="Y36" t="n">
         <v>5</v>
       </c>
-      <c r="Q36" t="n">
-        <v>0.02323891239493425</v>
-      </c>
-      <c r="R36" t="n">
-        <v>0.03135653123563305</v>
-      </c>
-      <c r="S36" t="n">
-        <v>1.547665565920039</v>
-      </c>
-      <c r="T36" t="n">
-        <v>0.5141790729750663</v>
-      </c>
-      <c r="U36" t="n">
-        <v>0.3977749888856326</v>
-      </c>
-      <c r="V36" t="n">
-        <v>0.2485255861053398</v>
-      </c>
-      <c r="W36" t="n">
-        <v>23.26682069967501</v>
-      </c>
-      <c r="X36" t="inlineStr">
-        <is>
-          <t>success</t>
-        </is>
-      </c>
-      <c r="Y36" t="inlineStr"/>
+      <c r="Z36" t="n">
+        <v>0.0231752591089847</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>0.03125809778650628</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>1.53835862347352</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>0.515228869315441</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>0.4966513999994883</v>
+      </c>
+      <c r="AE36" t="n">
+        <v>0.2456299583318469</v>
+      </c>
+      <c r="AF36" t="n">
+        <v>0.4966513999994883</v>
+      </c>
+      <c r="AG36" t="n">
+        <v>0.2456299583318469</v>
+      </c>
+      <c r="AH36" t="n">
+        <v>26.72212889992807</v>
+      </c>
+      <c r="AI36" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="AJ36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>architecture_tuning_esn_v1_20260329T153803Z</t>
+          <t>architecture_tuning_esn_v1_20260819T074659Z</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3996,49 +4576,64 @@
       <c r="L37" t="n">
         <v>0.95</v>
       </c>
-      <c r="M37" t="inlineStr">
+      <c r="M37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
+      <c r="O37" t="inlineStr"/>
+      <c r="P37" t="inlineStr"/>
+      <c r="Q37" t="inlineStr"/>
+      <c r="R37" t="inlineStr"/>
+      <c r="S37" t="inlineStr"/>
+      <c r="T37" t="inlineStr"/>
+      <c r="U37" t="inlineStr"/>
+      <c r="V37" t="inlineStr">
         <is>
           <t>{"compare_group_id": "esn_grp_004", "model_params": {"g_end": 0.95, "g_start": 1.28, "input_scale": 0.12, "leak_rate": 0.9, "n_reservoir": 160, "ridge_alpha": 0.001, "seed": 2026, "spectral_radius": 0.92}, "runtime_params": {}}</t>
         </is>
       </c>
-      <c r="N37" t="inlineStr">
+      <c r="W37" t="inlineStr">
         <is>
           <t>{'model_params': {'n_reservoir': 160, 'spectral_radius': 0.92, 'input_scale': 0.12, 'leak_rate': 0.9, 'ridge_alpha': 0.001, 'g_start': 1.28, 'g_end': 0.95, 'seed': 2026}, 'runtime_params': {}, 'compare_group_id': 'esn_grp_004'}</t>
         </is>
       </c>
-      <c r="O37" t="n">
+      <c r="X37" t="n">
         <v>12</v>
       </c>
-      <c r="P37" t="n">
+      <c r="Y37" t="n">
         <v>20</v>
       </c>
-      <c r="Q37" t="n">
-        <v>0.04779689889808188</v>
-      </c>
-      <c r="R37" t="n">
-        <v>0.06159255907450345</v>
-      </c>
-      <c r="S37" t="n">
-        <v>3.190531812006249</v>
-      </c>
-      <c r="T37" t="n">
-        <v>0.4964937542940454</v>
-      </c>
-      <c r="U37" t="n">
-        <v>0.198733247234486</v>
-      </c>
-      <c r="V37" t="n">
-        <v>0.123528597213509</v>
-      </c>
-      <c r="W37" t="n">
-        <v>11.60142640012782</v>
-      </c>
-      <c r="X37" t="inlineStr">
-        <is>
-          <t>success</t>
-        </is>
-      </c>
-      <c r="Y37" t="inlineStr"/>
+      <c r="Z37" t="n">
+        <v>0.04729870869361281</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>0.06107169491823438</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>3.122324366699958</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>0.5160731896222429</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>0.2478681194447239</v>
+      </c>
+      <c r="AE37" t="n">
+        <v>0.1237030333326806</v>
+      </c>
+      <c r="AF37" t="n">
+        <v>0.2478681194447239</v>
+      </c>
+      <c r="AG37" t="n">
+        <v>0.1237030333326806</v>
+      </c>
+      <c r="AH37" t="n">
+        <v>13.37656149998656</v>
+      </c>
+      <c r="AI37" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="AJ37" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4121,22 +4716,22 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.01063166951982817</v>
+        <v>0.01053668461277604</v>
       </c>
       <c r="E2" t="n">
-        <v>0.01473016845151821</v>
+        <v>0.01453785894297915</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6957751801022097</v>
+        <v>0.6912171500733124</v>
       </c>
       <c r="G2" t="n">
-        <v>0.5007984906462047</v>
+        <v>0.4997423890500503</v>
       </c>
       <c r="H2" t="n">
-        <v>0.4839761277673664</v>
+        <v>0.6039024305553337</v>
       </c>
       <c r="I2" t="n">
-        <v>0.3019129888853059</v>
+        <v>0.3015761888879449</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -4159,22 +4754,22 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.02448029634417161</v>
+        <v>0.02409615005911813</v>
       </c>
       <c r="E3" t="n">
-        <v>0.03303877311228397</v>
+        <v>0.03252101077839731</v>
       </c>
       <c r="F3" t="n">
-        <v>1.66257235186108</v>
+        <v>1.61258618294362</v>
       </c>
       <c r="G3" t="n">
-        <v>0.5070071814842384</v>
+        <v>0.5095891037671815</v>
       </c>
       <c r="H3" t="n">
-        <v>0.2449938638924828</v>
+        <v>0.306419275000533</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1533631916714108</v>
+        <v>0.1533095777784992</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -4197,22 +4792,22 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.04753378675828981</v>
+        <v>0.04702765687279834</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0613365172320566</v>
+        <v>0.06090067397102622</v>
       </c>
       <c r="F4" t="n">
-        <v>3.176695087997378</v>
+        <v>3.116190669808164</v>
       </c>
       <c r="G4" t="n">
-        <v>0.5008160627354807</v>
+        <v>0.5192840357813747</v>
       </c>
       <c r="H4" t="n">
-        <v>0.1464355250096155</v>
+        <v>0.1841552027803522</v>
       </c>
       <c r="I4" t="n">
-        <v>0.09128993333110379</v>
+        <v>0.09077436111086473</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -4235,22 +4830,22 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.01034137666237373</v>
+        <v>0.01033782885424267</v>
       </c>
       <c r="E5" t="n">
-        <v>0.01429137021584309</v>
+        <v>0.01427699509113673</v>
       </c>
       <c r="F5" t="n">
-        <v>0.6773609985805448</v>
+        <v>0.6774907023916258</v>
       </c>
       <c r="G5" t="n">
-        <v>0.507183991941757</v>
+        <v>0.504831246683341</v>
       </c>
       <c r="H5" t="n">
-        <v>0.5762485083347807</v>
+        <v>0.7252683361107807</v>
       </c>
       <c r="I5" t="n">
-        <v>0.357775774988113</v>
+        <v>0.3574251083320835</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -4273,22 +4868,22 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.02316324249823553</v>
+        <v>0.02312004313611583</v>
       </c>
       <c r="E6" t="n">
-        <v>0.03123117432855536</v>
+        <v>0.0311582045370359</v>
       </c>
       <c r="F6" t="n">
-        <v>1.539045132707624</v>
+        <v>1.533552753962528</v>
       </c>
       <c r="G6" t="n">
-        <v>0.5135002732595695</v>
+        <v>0.5146844711194423</v>
       </c>
       <c r="H6" t="n">
-        <v>0.3419074166740756</v>
+        <v>0.4276182222214023</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2125711499894452</v>
+        <v>0.2106089944443536</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -4311,22 +4906,22 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.04768954333195959</v>
+        <v>0.04711416704780948</v>
       </c>
       <c r="E7" t="n">
-        <v>0.06154801970929421</v>
+        <v>0.06091774773536213</v>
       </c>
       <c r="F7" t="n">
-        <v>3.187976837845405</v>
+        <v>3.116200502491193</v>
       </c>
       <c r="G7" t="n">
-        <v>0.4947285293643163</v>
+        <v>0.515789004768522</v>
       </c>
       <c r="H7" t="n">
-        <v>0.1104597555434642</v>
+        <v>0.1376069416651767</v>
       </c>
       <c r="I7" t="n">
-        <v>0.06862462778291148</v>
+        <v>0.06961552500029534</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -4345,26 +4940,26 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>transient_chaotic_esn_g004</t>
+          <t>transient_chaotic_esn_g002</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.01036038484005677</v>
+        <v>0.01035982351147461</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0143152218649881</v>
+        <v>0.01431681599139619</v>
       </c>
       <c r="F8" t="n">
-        <v>0.6785631470407831</v>
+        <v>0.6796047078339283</v>
       </c>
       <c r="G8" t="n">
-        <v>0.5026751090713998</v>
+        <v>0.5016218472485754</v>
       </c>
       <c r="H8" t="n">
-        <v>0.7846242750011799</v>
+        <v>0.7282935416660621</v>
       </c>
       <c r="I8" t="n">
-        <v>0.4891986444514865</v>
+        <v>0.3656154750012017</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -4387,22 +4982,22 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.02323891239493425</v>
+        <v>0.0231752591089847</v>
       </c>
       <c r="E9" t="n">
-        <v>0.03135653123563305</v>
+        <v>0.03125809778650628</v>
       </c>
       <c r="F9" t="n">
-        <v>1.547665565920039</v>
+        <v>1.53835862347352</v>
       </c>
       <c r="G9" t="n">
-        <v>0.5141790729750663</v>
+        <v>0.515228869315441</v>
       </c>
       <c r="H9" t="n">
-        <v>0.3977749888856326</v>
+        <v>0.4966513999994883</v>
       </c>
       <c r="I9" t="n">
-        <v>0.2485255861053398</v>
+        <v>0.2456299583318469</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -4425,22 +5020,22 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.04759312950856324</v>
+        <v>0.04693362131005851</v>
       </c>
       <c r="E10" t="n">
-        <v>0.06147920160763922</v>
+        <v>0.0607416612846192</v>
       </c>
       <c r="F10" t="n">
-        <v>3.186062202025597</v>
+        <v>3.110853330250367</v>
       </c>
       <c r="G10" t="n">
-        <v>0.4970098605210711</v>
+        <v>0.5210938400520722</v>
       </c>
       <c r="H10" t="n">
-        <v>0.1501619861066704</v>
+        <v>0.1842380222228207</v>
       </c>
       <c r="I10" t="n">
-        <v>0.09320005834645902</v>
+        <v>0.09385663333361866</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -4459,7 +5054,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S13"/>
+  <dimension ref="A1:AL13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4480,80 +5075,175 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
+          <t>base_model_name</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>chaotic_model_name</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>secondary_model_name</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>base_candidate_id</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>chaotic_candidate_id</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>secondary_candidate_id</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>base_mae_mean</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>chaotic_mae_mean</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>secondary_mae_mean</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>chaotic_delta_mae_vs_base</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>secondary_delta_mae_vs_base</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>base_runtime_sec_mean</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>chaotic_runtime_sec_mean</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>secondary_runtime_sec_mean</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>chaotic_runtime_delta_sec_vs_base</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>secondary_runtime_delta_sec_vs_base</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>base_status</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>chaotic_status</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>secondary_status</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
           <t>esn_candidate_id</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>chaotic_esn_candidate_id</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>transient_chaotic_esn_candidate_id</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>esn_mae_mean</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>chaotic_esn_mae_mean</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>transient_chaotic_esn_mae_mean</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>chaotic_esn_delta_mae_vs_esn</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>transient_chaotic_esn_delta_mae_vs_esn</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>esn_runtime_sec_mean</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>chaotic_esn_runtime_sec_mean</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>transient_chaotic_esn_runtime_sec_mean</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>chaotic_esn_runtime_delta_sec_vs_esn</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>transient_chaotic_esn_runtime_delta_sec_vs_esn</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>esn_status</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="AK1" t="inlineStr">
         <is>
           <t>chaotic_esn_status</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="AL1" t="inlineStr">
         <is>
           <t>transient_chaotic_esn_status</t>
         </is>
@@ -4562,7 +5252,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>architecture_tuning_esn_v1_20260329T153803Z</t>
+          <t>architecture_tuning_esn_v1_20260819T074659Z</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -4575,60 +5265,135 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
+          <t>esn</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>chaotic_esn</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>transient_chaotic_esn</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
           <t>esn_g001</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>chaotic_esn_g001</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>transient_chaotic_esn_g001</t>
         </is>
       </c>
-      <c r="G2" t="n">
-        <v>0.01039454830934849</v>
-      </c>
-      <c r="H2" t="n">
-        <v>0.01099948145462603</v>
-      </c>
-      <c r="I2" t="n">
-        <v>0.01039239073857835</v>
-      </c>
       <c r="J2" t="n">
-        <v>0.0006049331452775367</v>
+        <v>0.01039268599059335</v>
       </c>
       <c r="K2" t="n">
-        <v>-2.15757077014038e-06</v>
+        <v>0.01086151268305805</v>
       </c>
       <c r="L2" t="n">
-        <v>0.7014511194397022</v>
+        <v>0.01039805345158544</v>
       </c>
       <c r="M2" t="n">
-        <v>0.7036931611138344</v>
+        <v>0.0004688266924646953</v>
       </c>
       <c r="N2" t="n">
-        <v>0.8694164000011775</v>
+        <v>5.367460992092635e-06</v>
       </c>
       <c r="O2" t="n">
-        <v>0.002242041674132222</v>
+        <v>0.8279049277791476</v>
       </c>
       <c r="P2" t="n">
-        <v>0.1679652805614753</v>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>success</t>
-        </is>
-      </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>success</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
+        <v>0.8127403388874275</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>1.001591083334562</v>
+      </c>
+      <c r="R2" t="n">
+        <v>-0.01516458889172012</v>
+      </c>
+      <c r="S2" t="n">
+        <v>0.173686155555414</v>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>esn_g001</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>chaotic_esn_g001</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>transient_chaotic_esn_g001</t>
+        </is>
+      </c>
+      <c r="Z2" t="n">
+        <v>0.01039268599059335</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>0.01086151268305805</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.01039805345158544</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>0.0004688266924646953</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>5.367460992092635e-06</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>0.8279049277791476</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>0.8127403388874275</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>1.001591083334562</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>-0.01516458889172012</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>0.173686155555414</v>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="AL2" t="inlineStr">
         <is>
           <t>success</t>
         </is>
@@ -4637,7 +5402,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>architecture_tuning_esn_v1_20260329T153803Z</t>
+          <t>architecture_tuning_esn_v1_20260819T074659Z</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -4650,60 +5415,135 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
+          <t>esn</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>chaotic_esn</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>transient_chaotic_esn</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
           <t>esn_g002</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>chaotic_esn_g002</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>transient_chaotic_esn_g002</t>
         </is>
       </c>
-      <c r="G3" t="n">
-        <v>0.01036761460764232</v>
-      </c>
-      <c r="H3" t="n">
-        <v>0.01063166951982817</v>
-      </c>
-      <c r="I3" t="n">
-        <v>0.01036084894920913</v>
-      </c>
       <c r="J3" t="n">
-        <v>0.0002640549121858543</v>
+        <v>0.0103593698603878</v>
       </c>
       <c r="K3" t="n">
-        <v>-6.76565843318877e-06</v>
+        <v>0.01053668461277604</v>
       </c>
       <c r="L3" t="n">
-        <v>0.7900457722199563</v>
+        <v>0.01035982351147461</v>
       </c>
       <c r="M3" t="n">
-        <v>0.7858891166526722</v>
+        <v>0.0001773147523882329</v>
       </c>
       <c r="N3" t="n">
-        <v>0.951009063894162</v>
+        <v>4.536510868052152e-07</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.004156655567284062</v>
+        <v>0.9347638472229138</v>
       </c>
       <c r="P3" t="n">
-        <v>0.1609632916742056</v>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>success</t>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>success</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
+        <v>0.9054786194432785</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>1.093909016667264</v>
+      </c>
+      <c r="R3" t="n">
+        <v>-0.02928522777963538</v>
+      </c>
+      <c r="S3" t="n">
+        <v>0.15914516944435</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>esn_g002</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>chaotic_esn_g002</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>transient_chaotic_esn_g002</t>
+        </is>
+      </c>
+      <c r="Z3" t="n">
+        <v>0.0103593698603878</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>0.01053668461277604</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.01035982351147461</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>0.0001773147523882329</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>4.536510868052152e-07</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>0.9347638472229138</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>0.9054786194432785</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>1.093909016667264</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>-0.02928522777963538</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>0.15914516944435</v>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="AL3" t="inlineStr">
         <is>
           <t>success</t>
         </is>
@@ -4712,7 +5552,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>architecture_tuning_esn_v1_20260329T153803Z</t>
+          <t>architecture_tuning_esn_v1_20260819T074659Z</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -4725,60 +5565,135 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
+          <t>esn</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>chaotic_esn</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>transient_chaotic_esn</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
           <t>esn_g003</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>chaotic_esn_g003</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>transient_chaotic_esn_g003</t>
         </is>
       </c>
-      <c r="G4" t="n">
-        <v>0.01034137666237373</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0.01228276575796864</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0.01038534467211033</v>
-      </c>
       <c r="J4" t="n">
-        <v>0.001941389095594907</v>
+        <v>0.01033782885424267</v>
       </c>
       <c r="K4" t="n">
-        <v>4.396800973659881e-05</v>
+        <v>0.01181863895057717</v>
       </c>
       <c r="L4" t="n">
-        <v>0.9340242833228937</v>
+        <v>0.01037423045476002</v>
       </c>
       <c r="M4" t="n">
-        <v>0.9367246194419245</v>
+        <v>0.001480810096334497</v>
       </c>
       <c r="N4" t="n">
-        <v>1.11747778055077</v>
+        <v>3.64016005173478e-05</v>
       </c>
       <c r="O4" t="n">
-        <v>0.002700336119030866</v>
+        <v>1.082693444442864</v>
       </c>
       <c r="P4" t="n">
-        <v>0.1834534972278762</v>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>success</t>
-        </is>
-      </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>success</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
+        <v>1.078285836110606</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>1.282469766670854</v>
+      </c>
+      <c r="R4" t="n">
+        <v>-0.004407608332258173</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0.19977632222799</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>esn_g003</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>chaotic_esn_g003</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>transient_chaotic_esn_g003</t>
+        </is>
+      </c>
+      <c r="Z4" t="n">
+        <v>0.01033782885424267</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>0.01181863895057717</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.01037423045476002</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>0.001480810096334497</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>3.64016005173478e-05</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>1.082693444442864</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>1.078285836110606</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>1.282469766670854</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>-0.004407608332258173</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>0.19977632222799</v>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="AL4" t="inlineStr">
         <is>
           <t>success</t>
         </is>
@@ -4787,7 +5702,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>architecture_tuning_esn_v1_20260329T153803Z</t>
+          <t>architecture_tuning_esn_v1_20260819T074659Z</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -4800,60 +5715,135 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
+          <t>esn</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>chaotic_esn</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>transient_chaotic_esn</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
           <t>esn_g004</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t>chaotic_esn_g004</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t>transient_chaotic_esn_g004</t>
         </is>
       </c>
-      <c r="G5" t="n">
-        <v>0.01035285634382571</v>
-      </c>
-      <c r="H5" t="n">
-        <v>0.01173511768353693</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0.01036038484005677</v>
-      </c>
       <c r="J5" t="n">
-        <v>0.001382261339711218</v>
+        <v>0.01034924599642818</v>
       </c>
       <c r="K5" t="n">
-        <v>7.528496231059417e-06</v>
+        <v>0.01149276160761661</v>
       </c>
       <c r="L5" t="n">
-        <v>1.092893177776002</v>
+        <v>0.01036178265425768</v>
       </c>
       <c r="M5" t="n">
-        <v>1.083999811118701</v>
+        <v>0.001143515611188427</v>
       </c>
       <c r="N5" t="n">
-        <v>1.273822919452666</v>
+        <v>1.253665782950317e-05</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.008893366657301005</v>
+        <v>1.241884444443309</v>
       </c>
       <c r="P5" t="n">
-        <v>0.180929741676664</v>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>success</t>
-        </is>
-      </c>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>success</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
+        <v>1.258620425000522</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>1.4627665444447</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0.01673598055721293</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0.2208821000013914</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>esn_g004</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>chaotic_esn_g004</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>transient_chaotic_esn_g004</t>
+        </is>
+      </c>
+      <c r="Z5" t="n">
+        <v>0.01034924599642818</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>0.01149276160761661</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.01036178265425768</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>0.001143515611188427</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>1.253665782950317e-05</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>1.241884444443309</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>1.258620425000522</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>1.4627665444447</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>0.01673598055721293</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>0.2208821000013914</v>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="AL5" t="inlineStr">
         <is>
           <t>success</t>
         </is>
@@ -4862,7 +5852,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>architecture_tuning_esn_v1_20260329T153803Z</t>
+          <t>architecture_tuning_esn_v1_20260819T074659Z</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -4875,60 +5865,135 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
+          <t>esn</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>chaotic_esn</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>transient_chaotic_esn</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
           <t>esn_g001</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t>chaotic_esn_g001</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="I6" t="inlineStr">
         <is>
           <t>transient_chaotic_esn_g001</t>
         </is>
       </c>
-      <c r="G6" t="n">
-        <v>0.02330462272532673</v>
-      </c>
-      <c r="H6" t="n">
-        <v>0.02479065188700861</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0.02340737598713888</v>
-      </c>
       <c r="J6" t="n">
-        <v>0.001486029161681883</v>
+        <v>0.02314510117570092</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0001027532618121454</v>
+        <v>0.02444551875570298</v>
       </c>
       <c r="L6" t="n">
-        <v>0.3573474972217809</v>
+        <v>0.02319330673262766</v>
       </c>
       <c r="M6" t="n">
-        <v>0.3578032055423439</v>
+        <v>0.001300417580002058</v>
       </c>
       <c r="N6" t="n">
-        <v>0.4426269472201562</v>
+        <v>4.820555692674686e-05</v>
       </c>
       <c r="O6" t="n">
-        <v>0.0004557083205629642</v>
+        <v>0.4224209805567322</v>
       </c>
       <c r="P6" t="n">
-        <v>0.08527944999837528</v>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>success</t>
-        </is>
-      </c>
-      <c r="R6" t="inlineStr">
-        <is>
-          <t>success</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
+        <v>0.4141354055540836</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0.5081704277779662</v>
+      </c>
+      <c r="R6" t="n">
+        <v>-0.008285575002648593</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0.08574944722123401</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>esn_g001</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>chaotic_esn_g001</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>transient_chaotic_esn_g001</t>
+        </is>
+      </c>
+      <c r="Z6" t="n">
+        <v>0.02314510117570092</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>0.02444551875570298</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.02319330673262766</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>0.001300417580002058</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>4.820555692674686e-05</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>0.4224209805567322</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>0.4141354055540836</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>0.5081704277779662</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>-0.008285575002648593</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>0.08574944722123401</v>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="AL6" t="inlineStr">
         <is>
           <t>success</t>
         </is>
@@ -4937,7 +6002,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>architecture_tuning_esn_v1_20260329T153803Z</t>
+          <t>architecture_tuning_esn_v1_20260819T074659Z</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -4950,60 +6015,135 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
+          <t>esn</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>chaotic_esn</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>transient_chaotic_esn</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
           <t>esn_g002</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="H7" t="inlineStr">
         <is>
           <t>chaotic_esn_g002</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="I7" t="inlineStr">
         <is>
           <t>transient_chaotic_esn_g002</t>
         </is>
       </c>
-      <c r="G7" t="n">
-        <v>0.02331971317695284</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0.02448029634417161</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0.02333578608268773</v>
-      </c>
       <c r="J7" t="n">
-        <v>0.001160583167218763</v>
+        <v>0.02314467726245402</v>
       </c>
       <c r="K7" t="n">
-        <v>1.607290573488532e-05</v>
+        <v>0.02409615005911813</v>
       </c>
       <c r="L7" t="n">
-        <v>0.4039260638625516</v>
+        <v>0.02317910650167047</v>
       </c>
       <c r="M7" t="n">
-        <v>0.3983570555638936</v>
+        <v>0.0009514727966641115</v>
       </c>
       <c r="N7" t="n">
-        <v>0.4846286139056448</v>
+        <v>3.442923921645469e-05</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.005569008298658085</v>
+        <v>0.4673772638893247</v>
       </c>
       <c r="P7" t="n">
-        <v>0.08070255004309318</v>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>success</t>
-        </is>
-      </c>
-      <c r="R7" t="inlineStr">
-        <is>
-          <t>success</t>
-        </is>
-      </c>
-      <c r="S7" t="inlineStr">
+        <v>0.4597288527790321</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0.5553824083326617</v>
+      </c>
+      <c r="R7" t="n">
+        <v>-0.007648411110292574</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0.08800514444333707</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>esn_g002</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>chaotic_esn_g002</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>transient_chaotic_esn_g002</t>
+        </is>
+      </c>
+      <c r="Z7" t="n">
+        <v>0.02314467726245402</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>0.02409615005911813</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.02317910650167047</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>0.0009514727966641115</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>3.442923921645469e-05</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>0.4673772638893247</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>0.4597288527790321</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>0.5553824083326617</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>-0.007648411110292574</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>0.08800514444333707</v>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="AL7" t="inlineStr">
         <is>
           <t>success</t>
         </is>
@@ -5012,7 +6152,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>architecture_tuning_esn_v1_20260329T153803Z</t>
+          <t>architecture_tuning_esn_v1_20260819T074659Z</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -5025,60 +6165,135 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
+          <t>esn</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>chaotic_esn</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>transient_chaotic_esn</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
           <t>esn_g003</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>chaotic_esn_g003</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="I8" t="inlineStr">
         <is>
           <t>transient_chaotic_esn_g003</t>
         </is>
       </c>
-      <c r="G8" t="n">
-        <v>0.02328078903148209</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0.0247903115117102</v>
-      </c>
-      <c r="I8" t="n">
-        <v>0.02339023900983392</v>
-      </c>
       <c r="J8" t="n">
-        <v>0.00150952248022811</v>
+        <v>0.02312797301778825</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0001094499783518277</v>
+        <v>0.02496988221433108</v>
       </c>
       <c r="L8" t="n">
-        <v>0.4768026388871172</v>
+        <v>0.02318381659998701</v>
       </c>
       <c r="M8" t="n">
-        <v>0.4738368833431095</v>
+        <v>0.001841909196542826</v>
       </c>
       <c r="N8" t="n">
-        <v>0.5700961722242128</v>
+        <v>5.584358219876129e-05</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.002965755544007742</v>
+        <v>0.5495290972204303</v>
       </c>
       <c r="P8" t="n">
-        <v>0.09329353333709561</v>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>success</t>
-        </is>
-      </c>
-      <c r="R8" t="inlineStr">
-        <is>
-          <t>success</t>
-        </is>
-      </c>
-      <c r="S8" t="inlineStr">
+        <v>0.5453257388892073</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0.6481100055562921</v>
+      </c>
+      <c r="R8" t="n">
+        <v>-0.004203358331222984</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0.09858090833586175</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>esn_g003</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>chaotic_esn_g003</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>transient_chaotic_esn_g003</t>
+        </is>
+      </c>
+      <c r="Z8" t="n">
+        <v>0.02312797301778825</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>0.02496988221433108</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0.02318381659998701</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>0.001841909196542826</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>5.584358219876129e-05</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>0.5495290972204303</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>0.5453257388892073</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>0.6481100055562921</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>-0.004203358331222984</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>0.09858090833586175</v>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="AL8" t="inlineStr">
         <is>
           <t>success</t>
         </is>
@@ -5087,7 +6302,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>architecture_tuning_esn_v1_20260329T153803Z</t>
+          <t>architecture_tuning_esn_v1_20260819T074659Z</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -5100,60 +6315,135 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
+          <t>esn</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>chaotic_esn</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>transient_chaotic_esn</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
           <t>esn_g004</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>chaotic_esn_g004</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="I9" t="inlineStr">
         <is>
           <t>transient_chaotic_esn_g004</t>
         </is>
       </c>
-      <c r="G9" t="n">
-        <v>0.02316324249823553</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0.02544268153310842</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0.02323891239493425</v>
-      </c>
       <c r="J9" t="n">
-        <v>0.00227943903487289</v>
+        <v>0.02312004313611583</v>
       </c>
       <c r="K9" t="n">
-        <v>7.566989669871918e-05</v>
+        <v>0.02498120703078086</v>
       </c>
       <c r="L9" t="n">
-        <v>0.5544785666635208</v>
+        <v>0.0231752591089847</v>
       </c>
       <c r="M9" t="n">
-        <v>0.5471194583353484</v>
+        <v>0.001861163894665025</v>
       </c>
       <c r="N9" t="n">
-        <v>0.6463005749909724</v>
+        <v>5.521597286886268e-05</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.007359108328172437</v>
+        <v>0.6382272166657559</v>
       </c>
       <c r="P9" t="n">
-        <v>0.09182200832745158</v>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>success</t>
-        </is>
-      </c>
-      <c r="R9" t="inlineStr">
-        <is>
-          <t>success</t>
-        </is>
-      </c>
-      <c r="S9" t="inlineStr">
+        <v>0.6426622861116711</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0.7422813583313352</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0.004435069445915207</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0.1040541416655794</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>esn_g004</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>chaotic_esn_g004</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>transient_chaotic_esn_g004</t>
+        </is>
+      </c>
+      <c r="Z9" t="n">
+        <v>0.02312004313611583</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>0.02498120703078086</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0.0231752591089847</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>0.001861163894665025</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>5.521597286886268e-05</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>0.6382272166657559</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>0.6426622861116711</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>0.7422813583313352</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>0.004435069445915207</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>0.1040541416655794</v>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="AL9" t="inlineStr">
         <is>
           <t>success</t>
         </is>
@@ -5162,7 +6452,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>architecture_tuning_esn_v1_20260329T153803Z</t>
+          <t>architecture_tuning_esn_v1_20260819T074659Z</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -5175,60 +6465,135 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
+          <t>esn</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>chaotic_esn</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>transient_chaotic_esn</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
           <t>esn_g001</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="H10" t="inlineStr">
         <is>
           <t>chaotic_esn_g001</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="I10" t="inlineStr">
         <is>
           <t>transient_chaotic_esn_g001</t>
         </is>
       </c>
-      <c r="G10" t="n">
-        <v>0.04768954333195959</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0.04991233402531026</v>
-      </c>
-      <c r="I10" t="n">
-        <v>0.04764358963206822</v>
-      </c>
       <c r="J10" t="n">
-        <v>0.002222790693350671</v>
+        <v>0.04711416704780948</v>
       </c>
       <c r="K10" t="n">
-        <v>-4.595369989137538e-05</v>
+        <v>0.04893294690021489</v>
       </c>
       <c r="L10" t="n">
-        <v>0.1790843833263757</v>
+        <v>0.04699795988071519</v>
       </c>
       <c r="M10" t="n">
-        <v>0.179680341673601</v>
+        <v>0.001818779852405403</v>
       </c>
       <c r="N10" t="n">
-        <v>0.2229723694423835</v>
+        <v>-0.0001162071670942899</v>
       </c>
       <c r="O10" t="n">
-        <v>0.0005959583472253116</v>
+        <v>0.2072224666654721</v>
       </c>
       <c r="P10" t="n">
-        <v>0.04388798611600783</v>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>success</t>
-        </is>
-      </c>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>success</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr">
+        <v>0.2031672416661523</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0.2530956777781184</v>
+      </c>
+      <c r="R10" t="n">
+        <v>-0.004055224999319762</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0.04587321111264631</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>esn_g001</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>chaotic_esn_g001</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>transient_chaotic_esn_g001</t>
+        </is>
+      </c>
+      <c r="Z10" t="n">
+        <v>0.04711416704780948</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>0.04893294690021489</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0.04699795988071519</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>0.001818779852405403</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>-0.0001162071670942899</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>0.2072224666654721</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>0.2031672416661523</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>0.2530956777781184</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>-0.004055224999319762</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>0.04587321111264631</v>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="AL10" t="inlineStr">
         <is>
           <t>success</t>
         </is>
@@ -5237,7 +6602,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>architecture_tuning_esn_v1_20260329T153803Z</t>
+          <t>architecture_tuning_esn_v1_20260819T074659Z</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -5250,60 +6615,135 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
+          <t>esn</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>chaotic_esn</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>transient_chaotic_esn</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
           <t>esn_g002</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="H11" t="inlineStr">
         <is>
           <t>chaotic_esn_g002</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="I11" t="inlineStr">
         <is>
           <t>transient_chaotic_esn_g002</t>
         </is>
       </c>
-      <c r="G11" t="n">
-        <v>0.04771501819164769</v>
-      </c>
-      <c r="H11" t="n">
-        <v>0.05003216624556578</v>
-      </c>
-      <c r="I11" t="n">
-        <v>0.04759312950856324</v>
-      </c>
       <c r="J11" t="n">
-        <v>0.00231714805391809</v>
+        <v>0.04715806020447764</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.0001218886830844507</v>
+        <v>0.04857259972828862</v>
       </c>
       <c r="L11" t="n">
-        <v>0.2006568388896994</v>
+        <v>0.04693362131005851</v>
       </c>
       <c r="M11" t="n">
-        <v>0.1994017027900554</v>
+        <v>0.00141453952381098</v>
       </c>
       <c r="N11" t="n">
-        <v>0.2433620444531294</v>
+        <v>-0.0002244388944191295</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.001255136099644005</v>
+        <v>0.2326540805552213</v>
       </c>
       <c r="P11" t="n">
-        <v>0.04270520556342994</v>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>success</t>
-        </is>
-      </c>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>success</t>
-        </is>
-      </c>
-      <c r="S11" t="inlineStr">
+        <v>0.2274689777764757</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0.2780946555564394</v>
+      </c>
+      <c r="R11" t="n">
+        <v>-0.005185102778745621</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0.04544057500121806</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>esn_g002</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>chaotic_esn_g002</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>transient_chaotic_esn_g002</t>
+        </is>
+      </c>
+      <c r="Z11" t="n">
+        <v>0.04715806020447764</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>0.04857259972828862</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0.04693362131005851</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>0.00141453952381098</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>-0.0002244388944191295</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>0.2326540805552213</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>0.2274689777764757</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>0.2780946555564394</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>-0.005185102778745621</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>0.04544057500121806</v>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="AL11" t="inlineStr">
         <is>
           <t>success</t>
         </is>
@@ -5312,7 +6752,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>architecture_tuning_esn_v1_20260329T153803Z</t>
+          <t>architecture_tuning_esn_v1_20260819T074659Z</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -5325,60 +6765,135 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
+          <t>esn</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>chaotic_esn</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>transient_chaotic_esn</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
           <t>esn_g003</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="H12" t="inlineStr">
         <is>
           <t>chaotic_esn_g003</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="I12" t="inlineStr">
         <is>
           <t>transient_chaotic_esn_g003</t>
         </is>
       </c>
-      <c r="G12" t="n">
-        <v>0.04776794316810811</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0.04753378675828981</v>
-      </c>
-      <c r="I12" t="n">
-        <v>0.04778486189622352</v>
-      </c>
       <c r="J12" t="n">
-        <v>-0.0002341564098183035</v>
+        <v>0.04725686013581028</v>
       </c>
       <c r="K12" t="n">
-        <v>1.69187281154129e-05</v>
+        <v>0.04702765687279834</v>
       </c>
       <c r="L12" t="n">
-        <v>0.2385562055504933</v>
+        <v>0.04726913975724174</v>
       </c>
       <c r="M12" t="n">
-        <v>0.2377254583407193</v>
+        <v>-0.0002292032630119428</v>
       </c>
       <c r="N12" t="n">
-        <v>0.2851679250015877</v>
+        <v>1.227962143145189e-05</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.000830747209773941</v>
+        <v>0.2724378833336232</v>
       </c>
       <c r="P12" t="n">
-        <v>0.04661171945109444</v>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>success</t>
-        </is>
-      </c>
-      <c r="R12" t="inlineStr">
-        <is>
-          <t>success</t>
-        </is>
-      </c>
-      <c r="S12" t="inlineStr">
+        <v>0.274929563891217</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0.3242096444462529</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0.002491680557593801</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0.05177176111262977</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>esn_g003</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>chaotic_esn_g003</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>transient_chaotic_esn_g003</t>
+        </is>
+      </c>
+      <c r="Z12" t="n">
+        <v>0.04725686013581028</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>0.04702765687279834</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>0.04726913975724174</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>-0.0002292032630119428</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>1.227962143145189e-05</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>0.2724378833336232</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>0.274929563891217</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>0.3242096444462529</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>0.002491680557593801</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>0.05177176111262977</v>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="AL12" t="inlineStr">
         <is>
           <t>success</t>
         </is>
@@ -5387,7 +6902,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>architecture_tuning_esn_v1_20260329T153803Z</t>
+          <t>architecture_tuning_esn_v1_20260819T074659Z</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -5400,60 +6915,135 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
+          <t>esn</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>chaotic_esn</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>transient_chaotic_esn</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
           <t>esn_g004</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="H13" t="inlineStr">
         <is>
           <t>chaotic_esn_g004</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="I13" t="inlineStr">
         <is>
           <t>transient_chaotic_esn_g004</t>
         </is>
       </c>
-      <c r="G13" t="n">
-        <v>0.04772484293579016</v>
-      </c>
-      <c r="H13" t="n">
-        <v>0.04764911907732803</v>
-      </c>
-      <c r="I13" t="n">
-        <v>0.04779689889808188</v>
-      </c>
       <c r="J13" t="n">
-        <v>-7.572385846212754e-05</v>
+        <v>0.04722205340026055</v>
       </c>
       <c r="K13" t="n">
-        <v>7.205596229172689e-05</v>
+        <v>0.04734201020209549</v>
       </c>
       <c r="L13" t="n">
-        <v>0.2741301555490483</v>
+        <v>0.04729870869361281</v>
       </c>
       <c r="M13" t="n">
-        <v>0.2753297638846561</v>
+        <v>0.0001199568018349362</v>
       </c>
       <c r="N13" t="n">
-        <v>0.322261844447995</v>
+        <v>7.665529335225407e-05</v>
       </c>
       <c r="O13" t="n">
-        <v>0.001199608335607782</v>
+        <v>0.3166529027779083</v>
       </c>
       <c r="P13" t="n">
-        <v>0.04813168889894665</v>
-      </c>
-      <c r="Q13" t="inlineStr">
-        <is>
-          <t>success</t>
-        </is>
-      </c>
-      <c r="R13" t="inlineStr">
-        <is>
-          <t>success</t>
-        </is>
-      </c>
-      <c r="S13" t="inlineStr">
+        <v>0.3171306611123631</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0.3715711527774045</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0.0004777583344548475</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0.05491824999949624</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>esn_g004</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>chaotic_esn_g004</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>transient_chaotic_esn_g004</t>
+        </is>
+      </c>
+      <c r="Z13" t="n">
+        <v>0.04722205340026055</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>0.04734201020209549</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>0.04729870869361281</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>0.0001199568018349362</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>7.665529335225407e-05</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>0.3166529027779083</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>0.3171306611123631</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>0.3715711527774045</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>0.0004777583344548475</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>0.05491824999949624</v>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="AL13" t="inlineStr">
         <is>
           <t>success</t>
         </is>
@@ -5538,7 +7128,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>architecture_tuning_esn_v1_20260329T153803Z</t>
+          <t>architecture_tuning_esn_v1_20260819T074659Z</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -5548,33 +7138,33 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>chaotic_esn_g003</t>
+          <t>chaotic_esn_g002</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.02820228800932288</v>
+        <v>0.02773514480006093</v>
       </c>
       <c r="E2" t="n">
-        <v>0.03743838242297103</v>
+        <v>0.03696568776732975</v>
       </c>
       <c r="F2" t="n">
-        <v>1.882370987521124</v>
+        <v>1.847625638623427</v>
       </c>
       <c r="G2" t="n">
-        <v>0.5049045619139999</v>
+        <v>0.5074101375438551</v>
       </c>
       <c r="H2" t="n">
-        <v>0.3386673259298766</v>
+        <v>0.3538351870365322</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2107616611120412</v>
+        <v>0.1770569629630633</v>
       </c>
       <c r="J2" t="n">
-        <v>19.77944353350904</v>
+        <v>19.11211739998544</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>esn_grp_003</t>
+          <t>esn_grp_002</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -5586,7 +7176,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>architecture_tuning_esn_v1_20260329T153803Z</t>
+          <t>architecture_tuning_esn_v1_20260819T074659Z</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -5596,33 +7186,33 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>esn_g004</t>
+          <t>esn_g001</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.02708031392595047</v>
+        <v>0.02688398473803458</v>
       </c>
       <c r="E3" t="n">
-        <v>0.03569045425400135</v>
+        <v>0.03549403190683065</v>
       </c>
       <c r="F3" t="n">
-        <v>1.799980602176624</v>
+        <v>1.777841596169583</v>
       </c>
       <c r="G3" t="n">
-        <v>0.5036647406265818</v>
+        <v>0.5124012686382303</v>
       </c>
       <c r="H3" t="n">
-        <v>0.3956744925936046</v>
+        <v>0.3243366101847238</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2448261407359193</v>
+        <v>0.1615128481490602</v>
       </c>
       <c r="J3" t="n">
-        <v>23.05802279986286</v>
+        <v>17.49058050001622</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>esn_grp_004</t>
+          <t>esn_grp_001</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -5634,7 +7224,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>architecture_tuning_esn_v1_20260329T153803Z</t>
+          <t>architecture_tuning_esn_v1_20260819T074659Z</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -5648,25 +7238,25 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.02709658818015337</v>
+        <v>0.0268241837744012</v>
       </c>
       <c r="E4" t="n">
-        <v>0.03575111007266724</v>
+        <v>0.03544144351972784</v>
       </c>
       <c r="F4" t="n">
-        <v>1.809845599303096</v>
+        <v>1.776576380209354</v>
       </c>
       <c r="G4" t="n">
-        <v>0.5035695704535579</v>
+        <v>0.5141611277520614</v>
       </c>
       <c r="H4" t="n">
-        <v>0.3442249231523385</v>
+        <v>0.4275162277779061</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2154416509319735</v>
+        <v>0.2149457990742155</v>
       </c>
       <c r="J4" t="n">
-        <v>20.14799666703523</v>
+        <v>23.12863296667638</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -5713,7 +7303,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>architecture_tuning_esn_v1_20260329T153803Z</t>
+          <t>architecture_tuning_esn_v1_20260819T074659Z</t>
         </is>
       </c>
     </row>
